--- a/research/traditional_assets/database/data/malta/malta_software_internet.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_software_internet.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1148627349403204</v>
+        <v>0.1144899653680293</v>
       </c>
       <c r="C2">
-        <v>107.254242860921</v>
+        <v>106.5317958139383</v>
       </c>
       <c r="D2">
-        <v>101.634242860921</v>
+        <v>102.1857958139383</v>
       </c>
       <c r="E2">
-        <v>-54</v>
+        <v>-52.726</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.274</v>
       </c>
       <c r="G2">
         <v>5.62</v>
@@ -1451,28 +1451,28 @@
         <v>11.52</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.06408219999999999</v>
       </c>
       <c r="N2">
-        <v>11.52</v>
+        <v>11.4559178</v>
       </c>
       <c r="O2">
-        <v>4.032</v>
+        <v>4.00957123</v>
       </c>
       <c r="P2">
-        <v>7.488</v>
+        <v>7.44634657</v>
       </c>
       <c r="Q2">
-        <v>7.667999999999999</v>
+        <v>7.62634657</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1148627349403204</v>
+        <v>0.1153161771394235</v>
       </c>
       <c r="T2">
-        <v>1.264908244262673</v>
+        <v>1.273213197381569</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>179.7691090505632</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1144899653680293</v>
+        <v>0.1141171957957381</v>
       </c>
       <c r="C3">
-        <v>106.5317958139383</v>
+        <v>105.8153678125561</v>
       </c>
       <c r="D3">
-        <v>102.1857958139383</v>
+        <v>102.7433678125561</v>
       </c>
       <c r="E3">
-        <v>-52.726</v>
+        <v>-51.452</v>
       </c>
       <c r="F3">
-        <v>1.274</v>
+        <v>2.548</v>
       </c>
       <c r="G3">
         <v>5.62</v>
@@ -1533,28 +1533,28 @@
         <v>11.52</v>
       </c>
       <c r="M3">
-        <v>0.06408219999999999</v>
+        <v>0.1281644</v>
       </c>
       <c r="N3">
-        <v>11.4559178</v>
+        <v>11.3918356</v>
       </c>
       <c r="O3">
-        <v>4.00957123</v>
+        <v>3.98714246</v>
       </c>
       <c r="P3">
-        <v>7.44634657</v>
+        <v>7.404693140000001</v>
       </c>
       <c r="Q3">
-        <v>7.62634657</v>
+        <v>7.584693140000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1153161771394235</v>
+        <v>0.1157788732609573</v>
       </c>
       <c r="T3">
-        <v>1.273213197381569</v>
+        <v>1.281687639339627</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>179.7691090505632</v>
+        <v>89.8845545252816</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1141171957957381</v>
+        <v>0.113744426223447</v>
       </c>
       <c r="C4">
-        <v>105.8153678125561</v>
+        <v>105.1050579252562</v>
       </c>
       <c r="D4">
-        <v>102.7433678125561</v>
+        <v>103.3070579252562</v>
       </c>
       <c r="E4">
-        <v>-51.452</v>
+        <v>-50.178</v>
       </c>
       <c r="F4">
-        <v>2.548</v>
+        <v>3.822</v>
       </c>
       <c r="G4">
         <v>5.62</v>
@@ -1615,28 +1615,28 @@
         <v>11.52</v>
       </c>
       <c r="M4">
-        <v>0.1281644</v>
+        <v>0.1922466</v>
       </c>
       <c r="N4">
-        <v>11.3918356</v>
+        <v>11.3277534</v>
       </c>
       <c r="O4">
-        <v>3.98714246</v>
+        <v>3.96471369</v>
       </c>
       <c r="P4">
-        <v>7.404693140000001</v>
+        <v>7.363039709999999</v>
       </c>
       <c r="Q4">
-        <v>7.584693140000001</v>
+        <v>7.543039709999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1157788732609573</v>
+        <v>0.1162511095087083</v>
       </c>
       <c r="T4">
-        <v>1.281687639339627</v>
+        <v>1.290336812059706</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>89.8845545252816</v>
+        <v>59.92303635018772</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.113744426223447</v>
+        <v>0.1133716566511559</v>
       </c>
       <c r="C5">
-        <v>105.1050579252562</v>
+        <v>104.4009674066274</v>
       </c>
       <c r="D5">
-        <v>103.3070579252562</v>
+        <v>103.8769674066274</v>
       </c>
       <c r="E5">
-        <v>-50.178</v>
+        <v>-48.904</v>
       </c>
       <c r="F5">
-        <v>3.822</v>
+        <v>5.096</v>
       </c>
       <c r="G5">
         <v>5.62</v>
@@ -1697,28 +1697,28 @@
         <v>11.52</v>
       </c>
       <c r="M5">
-        <v>0.1922466</v>
+        <v>0.2563288</v>
       </c>
       <c r="N5">
-        <v>11.3277534</v>
+        <v>11.2636712</v>
       </c>
       <c r="O5">
-        <v>3.96471369</v>
+        <v>3.94228492</v>
       </c>
       <c r="P5">
-        <v>7.363039709999999</v>
+        <v>7.32138628</v>
       </c>
       <c r="Q5">
-        <v>7.543039709999999</v>
+        <v>7.501386279999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1162511095087083</v>
+        <v>0.1167331840116207</v>
       </c>
       <c r="T5">
-        <v>1.290336812059706</v>
+        <v>1.29916617587812</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>59.92303635018772</v>
+        <v>44.9422772626408</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1133716566511559</v>
+        <v>0.1129988870788648</v>
       </c>
       <c r="C6">
-        <v>104.4009674066274</v>
+        <v>103.7031997579998</v>
       </c>
       <c r="D6">
-        <v>103.8769674066274</v>
+        <v>104.4531997579998</v>
       </c>
       <c r="E6">
-        <v>-48.904</v>
+        <v>-47.63</v>
       </c>
       <c r="F6">
-        <v>5.096</v>
+        <v>6.370000000000001</v>
       </c>
       <c r="G6">
         <v>5.62</v>
@@ -1779,28 +1779,28 @@
         <v>11.52</v>
       </c>
       <c r="M6">
-        <v>0.2563288</v>
+        <v>0.3204110000000001</v>
       </c>
       <c r="N6">
-        <v>11.2636712</v>
+        <v>11.199589</v>
       </c>
       <c r="O6">
-        <v>3.94228492</v>
+        <v>3.91985615</v>
       </c>
       <c r="P6">
-        <v>7.32138628</v>
+        <v>7.27973285</v>
       </c>
       <c r="Q6">
-        <v>7.501386279999999</v>
+        <v>7.45973285</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1167331840116207</v>
+        <v>0.1172254074514366</v>
       </c>
       <c r="T6">
-        <v>1.29916617587812</v>
+        <v>1.30818142104008</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>44.9422772626408</v>
+        <v>35.95382181011263</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1129988870788648</v>
+        <v>0.1126261175065736</v>
       </c>
       <c r="C7">
-        <v>103.7031997579998</v>
+        <v>103.011860790109</v>
       </c>
       <c r="D7">
-        <v>104.4531997579998</v>
+        <v>105.035860790109</v>
       </c>
       <c r="E7">
-        <v>-47.63</v>
+        <v>-46.356</v>
       </c>
       <c r="F7">
-        <v>6.370000000000001</v>
+        <v>7.644000000000001</v>
       </c>
       <c r="G7">
         <v>5.62</v>
@@ -1861,28 +1861,28 @@
         <v>11.52</v>
       </c>
       <c r="M7">
-        <v>0.3204110000000001</v>
+        <v>0.3844932</v>
       </c>
       <c r="N7">
-        <v>11.199589</v>
+        <v>11.1355068</v>
       </c>
       <c r="O7">
-        <v>3.91985615</v>
+        <v>3.89742738</v>
       </c>
       <c r="P7">
-        <v>7.27973285</v>
+        <v>7.23807942</v>
       </c>
       <c r="Q7">
-        <v>7.45973285</v>
+        <v>7.41807942</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1172254074514366</v>
+        <v>0.1177281037303975</v>
       </c>
       <c r="T7">
-        <v>1.30818142104008</v>
+        <v>1.31738847992889</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.95382181011263</v>
+        <v>29.96151817509386</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1126261175065736</v>
+        <v>0.1122533479342826</v>
       </c>
       <c r="C8">
-        <v>103.011860790109</v>
+        <v>102.3270586878685</v>
       </c>
       <c r="D8">
-        <v>105.035860790109</v>
+        <v>105.6250586878684</v>
       </c>
       <c r="E8">
-        <v>-46.356</v>
+        <v>-45.082</v>
       </c>
       <c r="F8">
-        <v>7.644</v>
+        <v>8.917999999999999</v>
       </c>
       <c r="G8">
         <v>5.62</v>
@@ -1943,28 +1943,28 @@
         <v>11.52</v>
       </c>
       <c r="M8">
-        <v>0.3844932</v>
+        <v>0.4485754</v>
       </c>
       <c r="N8">
-        <v>11.1355068</v>
+        <v>11.0714246</v>
       </c>
       <c r="O8">
-        <v>3.89742738</v>
+        <v>3.87499861</v>
       </c>
       <c r="P8">
-        <v>7.23807942</v>
+        <v>7.19642599</v>
       </c>
       <c r="Q8">
-        <v>7.41807942</v>
+        <v>7.37642599</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1177281037303975</v>
+        <v>0.1182416106820242</v>
       </c>
       <c r="T8">
-        <v>1.31738847992889</v>
+        <v>1.326793540084126</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.96151817509386</v>
+        <v>25.6813012929376</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1122533479342825</v>
+        <v>0.1118805783619914</v>
       </c>
       <c r="C9">
-        <v>102.3270586878685</v>
+        <v>101.6489040773354</v>
       </c>
       <c r="D9">
-        <v>105.6250586878685</v>
+        <v>106.2209040773354</v>
       </c>
       <c r="E9">
-        <v>-45.082</v>
+        <v>-43.808</v>
       </c>
       <c r="F9">
-        <v>8.918000000000001</v>
+        <v>10.192</v>
       </c>
       <c r="G9">
         <v>5.62</v>
@@ -2025,28 +2025,28 @@
         <v>11.52</v>
       </c>
       <c r="M9">
-        <v>0.4485754</v>
+        <v>0.5126575999999999</v>
       </c>
       <c r="N9">
-        <v>11.0714246</v>
+        <v>11.0073424</v>
       </c>
       <c r="O9">
-        <v>3.87499861</v>
+        <v>3.852569839999999</v>
       </c>
       <c r="P9">
-        <v>7.19642599</v>
+        <v>7.15477256</v>
       </c>
       <c r="Q9">
-        <v>7.37642599</v>
+        <v>7.334772559999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1182416106820242</v>
+        <v>0.1187662808282515</v>
       </c>
       <c r="T9">
-        <v>1.326793540084126</v>
+        <v>1.336403058068824</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.6813012929376</v>
+        <v>22.4711386313204</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1118805783619914</v>
+        <v>0.1115078087897003</v>
       </c>
       <c r="C10">
-        <v>101.6489040773354</v>
+        <v>100.9775100949552</v>
       </c>
       <c r="D10">
-        <v>106.2209040773354</v>
+        <v>106.8235100949552</v>
       </c>
       <c r="E10">
-        <v>-43.808</v>
+        <v>-42.534</v>
       </c>
       <c r="F10">
-        <v>10.192</v>
+        <v>11.466</v>
       </c>
       <c r="G10">
         <v>5.62</v>
@@ -2107,28 +2107,28 @@
         <v>11.52</v>
       </c>
       <c r="M10">
-        <v>0.5126575999999999</v>
+        <v>0.5767397999999999</v>
       </c>
       <c r="N10">
-        <v>11.0073424</v>
+        <v>10.9432602</v>
       </c>
       <c r="O10">
-        <v>3.852569839999999</v>
+        <v>3.830141069999999</v>
       </c>
       <c r="P10">
-        <v>7.15477256</v>
+        <v>7.113119129999999</v>
       </c>
       <c r="Q10">
-        <v>7.334772559999999</v>
+        <v>7.293119129999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1187662808282515</v>
+        <v>0.1193024821864838</v>
       </c>
       <c r="T10">
-        <v>1.336403058068824</v>
+        <v>1.346223774250987</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.4711386313204</v>
+        <v>19.97434545006258</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1115078087897003</v>
+        <v>0.1111350392174092</v>
       </c>
       <c r="C11">
-        <v>100.9775100949552</v>
+        <v>100.3129924591768</v>
       </c>
       <c r="D11">
-        <v>106.8235100949552</v>
+        <v>107.4329924591768</v>
       </c>
       <c r="E11">
-        <v>-42.534</v>
+        <v>-41.26</v>
       </c>
       <c r="F11">
-        <v>11.466</v>
+        <v>12.74</v>
       </c>
       <c r="G11">
         <v>5.62</v>
@@ -2189,28 +2189,28 @@
         <v>11.52</v>
       </c>
       <c r="M11">
-        <v>0.5767397999999999</v>
+        <v>0.640822</v>
       </c>
       <c r="N11">
-        <v>10.9432602</v>
+        <v>10.879178</v>
       </c>
       <c r="O11">
-        <v>3.830141069999999</v>
+        <v>3.807712299999999</v>
       </c>
       <c r="P11">
-        <v>7.113119129999999</v>
+        <v>7.0714657</v>
       </c>
       <c r="Q11">
-        <v>7.293119129999999</v>
+        <v>7.2514657</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1193024821864838</v>
+        <v>0.1198505991304546</v>
       </c>
       <c r="T11">
-        <v>1.346223774250987</v>
+        <v>1.356262728570532</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.97434545006258</v>
+        <v>17.97691090505632</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1111350392174092</v>
+        <v>0.110762269645118</v>
       </c>
       <c r="C12">
-        <v>100.3129924591768</v>
+        <v>99.65546954453322</v>
       </c>
       <c r="D12">
-        <v>107.4329924591768</v>
+        <v>108.0494695445332</v>
       </c>
       <c r="E12">
-        <v>-41.26</v>
+        <v>-39.986</v>
       </c>
       <c r="F12">
-        <v>12.74</v>
+        <v>14.014</v>
       </c>
       <c r="G12">
         <v>5.62</v>
@@ -2271,28 +2271,28 @@
         <v>11.52</v>
       </c>
       <c r="M12">
-        <v>0.6408220000000001</v>
+        <v>0.7049042</v>
       </c>
       <c r="N12">
-        <v>10.879178</v>
+        <v>10.8150958</v>
       </c>
       <c r="O12">
-        <v>3.807712299999999</v>
+        <v>3.78528353</v>
       </c>
       <c r="P12">
-        <v>7.0714657</v>
+        <v>7.029812270000001</v>
       </c>
       <c r="Q12">
-        <v>7.2514657</v>
+        <v>7.20981227</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1198505991304546</v>
+        <v>0.1204110333091214</v>
       </c>
       <c r="T12">
-        <v>1.356262728570532</v>
+        <v>1.366527277369168</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.97691090505631</v>
+        <v>16.34264627732393</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.110762269645118</v>
+        <v>0.1103895000728269</v>
       </c>
       <c r="C13">
-        <v>99.65546954453322</v>
+        <v>99.00506245828831</v>
       </c>
       <c r="D13">
-        <v>108.0494695445332</v>
+        <v>108.6730624582883</v>
       </c>
       <c r="E13">
-        <v>-39.986</v>
+        <v>-38.712</v>
       </c>
       <c r="F13">
-        <v>14.014</v>
+        <v>15.288</v>
       </c>
       <c r="G13">
         <v>5.62</v>
@@ -2353,28 +2353,28 @@
         <v>11.52</v>
       </c>
       <c r="M13">
-        <v>0.7049042</v>
+        <v>0.7689864</v>
       </c>
       <c r="N13">
-        <v>10.8150958</v>
+        <v>10.7510136</v>
       </c>
       <c r="O13">
-        <v>3.78528353</v>
+        <v>3.76285476</v>
       </c>
       <c r="P13">
-        <v>7.029812270000001</v>
+        <v>6.988158840000001</v>
       </c>
       <c r="Q13">
-        <v>7.20981227</v>
+        <v>7.16815884</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1204110333091214</v>
+        <v>0.1209842046282124</v>
       </c>
       <c r="T13">
-        <v>1.366527277369168</v>
+        <v>1.377025111367773</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.34264627732393</v>
+        <v>14.98075908754693</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1103895000728269</v>
+        <v>0.1100167305005358</v>
       </c>
       <c r="C14">
-        <v>99.00506245828831</v>
+        <v>98.36189511975186</v>
       </c>
       <c r="D14">
-        <v>108.6730624582883</v>
+        <v>109.3038951197519</v>
       </c>
       <c r="E14">
-        <v>-38.712</v>
+        <v>-37.438</v>
       </c>
       <c r="F14">
-        <v>15.288</v>
+        <v>16.562</v>
       </c>
       <c r="G14">
         <v>5.62</v>
@@ -2435,28 +2435,28 @@
         <v>11.52</v>
       </c>
       <c r="M14">
-        <v>0.7689864</v>
+        <v>0.8330686</v>
       </c>
       <c r="N14">
-        <v>10.7510136</v>
+        <v>10.6869314</v>
       </c>
       <c r="O14">
-        <v>3.76285476</v>
+        <v>3.740425989999999</v>
       </c>
       <c r="P14">
-        <v>6.988158840000001</v>
+        <v>6.946505409999999</v>
       </c>
       <c r="Q14">
-        <v>7.16815884</v>
+        <v>7.126505409999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1209842046282124</v>
+        <v>0.1215705522994665</v>
       </c>
       <c r="T14">
-        <v>1.377025111367773</v>
+        <v>1.387764274883587</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.98075908754693</v>
+        <v>13.82839300388947</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1100167305005358</v>
+        <v>0.1097804609282447</v>
       </c>
       <c r="C15">
-        <v>98.36189511975186</v>
+        <v>97.49153685935514</v>
       </c>
       <c r="D15">
-        <v>109.3038951197519</v>
+        <v>109.7075368593551</v>
       </c>
       <c r="E15">
-        <v>-37.438</v>
+        <v>-36.164</v>
       </c>
       <c r="F15">
-        <v>16.562</v>
+        <v>17.836</v>
       </c>
       <c r="G15">
         <v>5.62</v>
@@ -2517,45 +2517,45 @@
         <v>11.52</v>
       </c>
       <c r="M15">
-        <v>0.8330686</v>
+        <v>0.9239048000000001</v>
       </c>
       <c r="N15">
-        <v>10.6869314</v>
+        <v>10.5960952</v>
       </c>
       <c r="O15">
-        <v>3.740425989999999</v>
+        <v>3.708633319999999</v>
       </c>
       <c r="P15">
-        <v>6.946505409999999</v>
+        <v>6.88746188</v>
       </c>
       <c r="Q15">
-        <v>7.126505409999999</v>
+        <v>7.06746188</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1215705522994665</v>
+        <v>0.1221705359630752</v>
       </c>
       <c r="T15">
-        <v>1.387764274883587</v>
+        <v>1.398753186388142</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.82839300388947</v>
+        <v>12.46881713354016</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1097804609282447</v>
+        <v>0.1094174413559536</v>
       </c>
       <c r="C16">
-        <v>97.49153685935514</v>
+        <v>96.84355988478555</v>
       </c>
       <c r="D16">
-        <v>109.7075368593551</v>
+        <v>110.3335598847855</v>
       </c>
       <c r="E16">
-        <v>-36.164</v>
+        <v>-34.89</v>
       </c>
       <c r="F16">
-        <v>17.836</v>
+        <v>19.11</v>
       </c>
       <c r="G16">
         <v>5.62</v>
@@ -2599,28 +2599,28 @@
         <v>11.52</v>
       </c>
       <c r="M16">
-        <v>0.9239048000000001</v>
+        <v>0.9898980000000002</v>
       </c>
       <c r="N16">
-        <v>10.5960952</v>
+        <v>10.530102</v>
       </c>
       <c r="O16">
-        <v>3.708633319999999</v>
+        <v>3.6855357</v>
       </c>
       <c r="P16">
-        <v>6.88746188</v>
+        <v>6.8445663</v>
       </c>
       <c r="Q16">
-        <v>7.06746188</v>
+        <v>7.0245663</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1221705359630752</v>
+        <v>0.1227846368893571</v>
       </c>
       <c r="T16">
-        <v>1.398753186388142</v>
+        <v>1.410000660516332</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.46881713354016</v>
+        <v>11.63756265797082</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1094174413559536</v>
+        <v>0.1090544217836624</v>
       </c>
       <c r="C17">
-        <v>96.84355988478555</v>
+        <v>96.20276845091109</v>
       </c>
       <c r="D17">
-        <v>110.3335598847855</v>
+        <v>110.9667684509111</v>
       </c>
       <c r="E17">
-        <v>-34.89</v>
+        <v>-33.616</v>
       </c>
       <c r="F17">
-        <v>19.11</v>
+        <v>20.384</v>
       </c>
       <c r="G17">
         <v>5.62</v>
@@ -2681,28 +2681,28 @@
         <v>11.52</v>
       </c>
       <c r="M17">
-        <v>0.9898979999999999</v>
+        <v>1.0558912</v>
       </c>
       <c r="N17">
-        <v>10.530102</v>
+        <v>10.4641088</v>
       </c>
       <c r="O17">
-        <v>3.6855357</v>
+        <v>3.66243808</v>
       </c>
       <c r="P17">
-        <v>6.8445663</v>
+        <v>6.801670720000001</v>
       </c>
       <c r="Q17">
-        <v>7.0245663</v>
+        <v>6.98167072</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1227846368893571</v>
+        <v>0.1234133592662648</v>
       </c>
       <c r="T17">
-        <v>1.410000660516332</v>
+        <v>1.421515931647575</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.63756265797082</v>
+        <v>10.91021499184764</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1090544217836624</v>
+        <v>0.1086914022113713</v>
       </c>
       <c r="C18">
-        <v>96.20276845091109</v>
+        <v>95.56928698611864</v>
       </c>
       <c r="D18">
-        <v>110.9667684509111</v>
+        <v>111.6072869861186</v>
       </c>
       <c r="E18">
-        <v>-33.616</v>
+        <v>-32.342</v>
       </c>
       <c r="F18">
-        <v>20.384</v>
+        <v>21.658</v>
       </c>
       <c r="G18">
         <v>5.62</v>
@@ -2763,28 +2763,28 @@
         <v>11.52</v>
       </c>
       <c r="M18">
-        <v>1.0558912</v>
+        <v>1.1218844</v>
       </c>
       <c r="N18">
-        <v>10.4641088</v>
+        <v>10.3981156</v>
       </c>
       <c r="O18">
-        <v>3.66243808</v>
+        <v>3.639340459999999</v>
       </c>
       <c r="P18">
-        <v>6.801670720000001</v>
+        <v>6.758775139999999</v>
       </c>
       <c r="Q18">
-        <v>6.98167072</v>
+        <v>6.938775139999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1234133592662648</v>
+        <v>0.1240572315799655</v>
       </c>
       <c r="T18">
-        <v>1.421515931647575</v>
+        <v>1.433308679191619</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.91021499184764</v>
+        <v>10.26843763938602</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1086914022113713</v>
+        <v>0.1085272826390802</v>
       </c>
       <c r="C19">
-        <v>95.56928698611864</v>
+        <v>94.58729613164674</v>
       </c>
       <c r="D19">
-        <v>111.6072869861186</v>
+        <v>111.8992961316467</v>
       </c>
       <c r="E19">
-        <v>-32.342</v>
+        <v>-31.068</v>
       </c>
       <c r="F19">
-        <v>21.658</v>
+        <v>22.932</v>
       </c>
       <c r="G19">
         <v>5.62</v>
@@ -2845,45 +2845,45 @@
         <v>11.52</v>
       </c>
       <c r="M19">
-        <v>1.1218844</v>
+        <v>1.226862</v>
       </c>
       <c r="N19">
-        <v>10.3981156</v>
+        <v>10.293138</v>
       </c>
       <c r="O19">
-        <v>3.639340459999999</v>
+        <v>3.602598299999999</v>
       </c>
       <c r="P19">
-        <v>6.758775139999999</v>
+        <v>6.6905397</v>
       </c>
       <c r="Q19">
-        <v>6.938775139999999</v>
+        <v>6.870539699999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1240572315799655</v>
+        <v>0.1247168080964393</v>
       </c>
       <c r="T19">
-        <v>1.433308679191619</v>
+        <v>1.445389054724542</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.26843763938602</v>
+        <v>9.389809122786424</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1085272826390802</v>
+        <v>0.1081753130667891</v>
       </c>
       <c r="C20">
-        <v>94.58729613164671</v>
+        <v>93.94471817127572</v>
       </c>
       <c r="D20">
-        <v>111.8992961316467</v>
+        <v>112.5307181712757</v>
       </c>
       <c r="E20">
-        <v>-31.068</v>
+        <v>-29.794</v>
       </c>
       <c r="F20">
-        <v>22.932</v>
+        <v>24.206</v>
       </c>
       <c r="G20">
         <v>5.62</v>
@@ -2927,28 +2927,28 @@
         <v>11.52</v>
       </c>
       <c r="M20">
-        <v>1.226862</v>
+        <v>1.295021</v>
       </c>
       <c r="N20">
-        <v>10.293138</v>
+        <v>10.224979</v>
       </c>
       <c r="O20">
-        <v>3.602598299999999</v>
+        <v>3.57874265</v>
       </c>
       <c r="P20">
-        <v>6.6905397</v>
+        <v>6.64623635</v>
       </c>
       <c r="Q20">
-        <v>6.870539699999999</v>
+        <v>6.826236349999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1247168080964393</v>
+        <v>0.125392670452826</v>
       </c>
       <c r="T20">
-        <v>1.445389054724542</v>
+        <v>1.457767711134821</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.389809122786426</v>
+        <v>8.89560864263977</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1081753130667891</v>
+        <v>0.107823343494498</v>
       </c>
       <c r="C21">
-        <v>93.94471817127572</v>
+        <v>93.30930658835891</v>
       </c>
       <c r="D21">
-        <v>112.5307181712757</v>
+        <v>113.1693065883589</v>
       </c>
       <c r="E21">
-        <v>-29.794</v>
+        <v>-28.52</v>
       </c>
       <c r="F21">
-        <v>24.206</v>
+        <v>25.48</v>
       </c>
       <c r="G21">
         <v>5.62</v>
@@ -3009,28 +3009,28 @@
         <v>11.52</v>
       </c>
       <c r="M21">
-        <v>1.295021</v>
+        <v>1.36318</v>
       </c>
       <c r="N21">
-        <v>10.224979</v>
+        <v>10.15682</v>
       </c>
       <c r="O21">
-        <v>3.57874265</v>
+        <v>3.554886999999999</v>
       </c>
       <c r="P21">
-        <v>6.64623635</v>
+        <v>6.601933000000001</v>
       </c>
       <c r="Q21">
-        <v>6.826236349999999</v>
+        <v>6.781933</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.125392670452826</v>
+        <v>0.1260854293681224</v>
       </c>
       <c r="T21">
-        <v>1.457767711134821</v>
+        <v>1.470455833955357</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.89560864263977</v>
+        <v>8.450828210507781</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.107823343494498</v>
+        <v>0.1074713739222068</v>
       </c>
       <c r="C22">
-        <v>93.30930658835891</v>
+        <v>92.6811840822937</v>
       </c>
       <c r="D22">
-        <v>113.1693065883589</v>
+        <v>113.8151840822937</v>
       </c>
       <c r="E22">
-        <v>-28.52</v>
+        <v>-27.246</v>
       </c>
       <c r="F22">
-        <v>25.48</v>
+        <v>26.754</v>
       </c>
       <c r="G22">
         <v>5.62</v>
@@ -3091,28 +3091,28 @@
         <v>11.52</v>
       </c>
       <c r="M22">
-        <v>1.36318</v>
+        <v>1.431339</v>
       </c>
       <c r="N22">
-        <v>10.15682</v>
+        <v>10.088661</v>
       </c>
       <c r="O22">
-        <v>3.554886999999999</v>
+        <v>3.53103135</v>
       </c>
       <c r="P22">
-        <v>6.601933000000001</v>
+        <v>6.557629650000001</v>
       </c>
       <c r="Q22">
-        <v>6.781933</v>
+        <v>6.737629650000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1260854293681224</v>
+        <v>0.1267957264838061</v>
       </c>
       <c r="T22">
-        <v>1.470455833955357</v>
+        <v>1.483465175075147</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.450828210507781</v>
+        <v>8.048407819531221</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1074713739222068</v>
+        <v>0.1071194043499157</v>
       </c>
       <c r="C23">
-        <v>92.6811840822937</v>
+        <v>92.06047616962515</v>
       </c>
       <c r="D23">
-        <v>113.8151840822937</v>
+        <v>114.4684761696251</v>
       </c>
       <c r="E23">
-        <v>-27.246</v>
+        <v>-25.972</v>
       </c>
       <c r="F23">
-        <v>26.754</v>
+        <v>28.028</v>
       </c>
       <c r="G23">
         <v>5.62</v>
@@ -3173,28 +3173,28 @@
         <v>11.52</v>
       </c>
       <c r="M23">
-        <v>1.431339</v>
+        <v>1.499498</v>
       </c>
       <c r="N23">
-        <v>10.088661</v>
+        <v>10.020502</v>
       </c>
       <c r="O23">
-        <v>3.53103135</v>
+        <v>3.5071757</v>
       </c>
       <c r="P23">
-        <v>6.557629650000001</v>
+        <v>6.513326300000001</v>
       </c>
       <c r="Q23">
-        <v>6.737629650000001</v>
+        <v>6.693326300000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1267957264838061</v>
+        <v>0.1275242363460458</v>
       </c>
       <c r="T23">
-        <v>1.483465175075147</v>
+        <v>1.496808089044163</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.048407819531221</v>
+        <v>7.682571100461622</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1071194043499157</v>
+        <v>0.1068870347776246</v>
       </c>
       <c r="C24">
-        <v>92.06047616962515</v>
+        <v>91.22190393175472</v>
       </c>
       <c r="D24">
-        <v>114.4684761696251</v>
+        <v>114.9039039317547</v>
       </c>
       <c r="E24">
-        <v>-25.972</v>
+        <v>-24.698</v>
       </c>
       <c r="F24">
-        <v>28.028</v>
+        <v>29.302</v>
       </c>
       <c r="G24">
         <v>5.62</v>
@@ -3255,45 +3255,45 @@
         <v>11.52</v>
       </c>
       <c r="M24">
-        <v>1.499498</v>
+        <v>1.5910986</v>
       </c>
       <c r="N24">
-        <v>10.020502</v>
+        <v>9.928901399999999</v>
       </c>
       <c r="O24">
-        <v>3.5071757</v>
+        <v>3.475115489999999</v>
       </c>
       <c r="P24">
-        <v>6.513326300000001</v>
+        <v>6.45378591</v>
       </c>
       <c r="Q24">
-        <v>6.693326300000001</v>
+        <v>6.633785909999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1275242363460458</v>
+        <v>0.1282716685423696</v>
       </c>
       <c r="T24">
-        <v>1.496808089044163</v>
+        <v>1.510497572207179</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.682571100461622</v>
+        <v>7.24028039494221</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1068870347776246</v>
+        <v>0.1065402652053335</v>
       </c>
       <c r="C25">
-        <v>91.22190393175472</v>
+        <v>90.60389674782652</v>
       </c>
       <c r="D25">
-        <v>114.9039039317547</v>
+        <v>115.5598967478265</v>
       </c>
       <c r="E25">
-        <v>-24.698</v>
+        <v>-23.424</v>
       </c>
       <c r="F25">
-        <v>29.302</v>
+        <v>30.576</v>
       </c>
       <c r="G25">
         <v>5.62</v>
@@ -3337,28 +3337,28 @@
         <v>11.52</v>
       </c>
       <c r="M25">
-        <v>1.5910986</v>
+        <v>1.6602768</v>
       </c>
       <c r="N25">
-        <v>9.928901399999999</v>
+        <v>9.859723199999999</v>
       </c>
       <c r="O25">
-        <v>3.475115489999999</v>
+        <v>3.45090312</v>
       </c>
       <c r="P25">
-        <v>6.45378591</v>
+        <v>6.40882008</v>
       </c>
       <c r="Q25">
-        <v>6.633785909999999</v>
+        <v>6.58882008</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1282716685423696</v>
+        <v>0.1290387700070177</v>
       </c>
       <c r="T25">
-        <v>1.510497572207179</v>
+        <v>1.524547304927116</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.24028039494221</v>
+        <v>6.938602045152951</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1065402652053335</v>
+        <v>0.1061934956330424</v>
       </c>
       <c r="C26">
-        <v>90.60389674782652</v>
+        <v>89.99342277077335</v>
       </c>
       <c r="D26">
-        <v>115.5598967478265</v>
+        <v>116.2234227707733</v>
       </c>
       <c r="E26">
-        <v>-23.424</v>
+        <v>-22.15</v>
       </c>
       <c r="F26">
-        <v>30.576</v>
+        <v>31.85</v>
       </c>
       <c r="G26">
         <v>5.62</v>
@@ -3419,28 +3419,28 @@
         <v>11.52</v>
       </c>
       <c r="M26">
-        <v>1.6602768</v>
+        <v>1.729455</v>
       </c>
       <c r="N26">
-        <v>9.859723199999999</v>
+        <v>9.790545</v>
       </c>
       <c r="O26">
-        <v>3.45090312</v>
+        <v>3.42669075</v>
       </c>
       <c r="P26">
-        <v>6.40882008</v>
+        <v>6.36385425</v>
       </c>
       <c r="Q26">
-        <v>6.58882008</v>
+        <v>6.54385425</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1290387700070177</v>
+        <v>0.1298263275107231</v>
       </c>
       <c r="T26">
-        <v>1.524547304927116</v>
+        <v>1.538971697186252</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.938602045152952</v>
+        <v>6.661057963346834</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1061934956330424</v>
+        <v>0.1058467260607512</v>
       </c>
       <c r="C27">
-        <v>89.99342277077335</v>
+        <v>89.39061251330247</v>
       </c>
       <c r="D27">
-        <v>116.2234227707733</v>
+        <v>116.8946125133025</v>
       </c>
       <c r="E27">
-        <v>-22.15</v>
+        <v>-20.876</v>
       </c>
       <c r="F27">
-        <v>31.85</v>
+        <v>33.124</v>
       </c>
       <c r="G27">
         <v>5.62</v>
@@ -3501,28 +3501,28 @@
         <v>11.52</v>
       </c>
       <c r="M27">
-        <v>1.729455</v>
+        <v>1.7986332</v>
       </c>
       <c r="N27">
-        <v>9.790545</v>
+        <v>9.721366799999998</v>
       </c>
       <c r="O27">
-        <v>3.42669075</v>
+        <v>3.402478379999999</v>
       </c>
       <c r="P27">
-        <v>6.36385425</v>
+        <v>6.318888419999999</v>
       </c>
       <c r="Q27">
-        <v>6.54385425</v>
+        <v>6.498888419999998</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1298263275107231</v>
+        <v>0.1306351703523665</v>
       </c>
       <c r="T27">
-        <v>1.538971697186252</v>
+        <v>1.553785937884824</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.661057963346834</v>
+        <v>6.404863426295032</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1058467260607512</v>
+        <v>0.1054999564884601</v>
       </c>
       <c r="C28">
-        <v>89.39061251330247</v>
+        <v>88.79559952047407</v>
       </c>
       <c r="D28">
-        <v>116.8946125133025</v>
+        <v>117.5735995204741</v>
       </c>
       <c r="E28">
-        <v>-20.876</v>
+        <v>-19.602</v>
       </c>
       <c r="F28">
-        <v>33.124</v>
+        <v>34.398</v>
       </c>
       <c r="G28">
         <v>5.62</v>
@@ -3583,28 +3583,28 @@
         <v>11.52</v>
       </c>
       <c r="M28">
-        <v>1.7986332</v>
+        <v>1.8678114</v>
       </c>
       <c r="N28">
-        <v>9.721366799999998</v>
+        <v>9.652188599999999</v>
       </c>
       <c r="O28">
-        <v>3.402478379999999</v>
+        <v>3.378266009999999</v>
       </c>
       <c r="P28">
-        <v>6.318888419999999</v>
+        <v>6.27392259</v>
       </c>
       <c r="Q28">
-        <v>6.498888419999998</v>
+        <v>6.453922589999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1306351703523665</v>
+        <v>0.1314661732718632</v>
       </c>
       <c r="T28">
-        <v>1.553785937884824</v>
+        <v>1.569006048191576</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.404863426295032</v>
+        <v>6.167646262358179</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1054999564884601</v>
+        <v>0.105335186916169</v>
       </c>
       <c r="C29">
-        <v>88.79559952047407</v>
+        <v>87.84699619274778</v>
       </c>
       <c r="D29">
-        <v>117.5735995204741</v>
+        <v>117.8989961927478</v>
       </c>
       <c r="E29">
-        <v>-19.602</v>
+        <v>-18.328</v>
       </c>
       <c r="F29">
-        <v>34.398</v>
+        <v>35.672</v>
       </c>
       <c r="G29">
         <v>5.62</v>
@@ -3665,45 +3665,45 @@
         <v>11.52</v>
       </c>
       <c r="M29">
-        <v>1.8678114</v>
+        <v>1.9726616</v>
       </c>
       <c r="N29">
-        <v>9.652188599999999</v>
+        <v>9.547338399999999</v>
       </c>
       <c r="O29">
-        <v>3.378266009999999</v>
+        <v>3.34156844</v>
       </c>
       <c r="P29">
-        <v>6.27392259</v>
+        <v>6.20576996</v>
       </c>
       <c r="Q29">
-        <v>6.453922589999999</v>
+        <v>6.385769959999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1314661732718632</v>
+        <v>0.1323202596057903</v>
       </c>
       <c r="T29">
-        <v>1.569006048191576</v>
+        <v>1.584648939340182</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.167646262358179</v>
+        <v>5.83982574608843</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.105335186916169</v>
+        <v>0.1049949173438779</v>
       </c>
       <c r="C30">
-        <v>87.84699619274778</v>
+        <v>87.25071385514451</v>
       </c>
       <c r="D30">
-        <v>117.8989961927478</v>
+        <v>118.5767138551445</v>
       </c>
       <c r="E30">
-        <v>-18.328</v>
+        <v>-17.05399999999999</v>
       </c>
       <c r="F30">
-        <v>35.672</v>
+        <v>36.94600000000001</v>
       </c>
       <c r="G30">
         <v>5.62</v>
@@ -3747,28 +3747,28 @@
         <v>11.52</v>
       </c>
       <c r="M30">
-        <v>1.9726616</v>
+        <v>2.0431138</v>
       </c>
       <c r="N30">
-        <v>9.547338399999999</v>
+        <v>9.476886199999999</v>
       </c>
       <c r="O30">
-        <v>3.34156844</v>
+        <v>3.316910169999999</v>
       </c>
       <c r="P30">
-        <v>6.20576996</v>
+        <v>6.159976029999999</v>
       </c>
       <c r="Q30">
-        <v>6.385769959999999</v>
+        <v>6.339976029999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1323202596057903</v>
+        <v>0.1331984047096871</v>
       </c>
       <c r="T30">
-        <v>1.584648939340182</v>
+        <v>1.600732475309875</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.83982574608843</v>
+        <v>5.638452444499174</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1049949173438779</v>
+        <v>0.1046546477715867</v>
       </c>
       <c r="C31">
-        <v>87.25071385514453</v>
+        <v>86.6622679997172</v>
       </c>
       <c r="D31">
-        <v>118.5767138551445</v>
+        <v>119.2622679997172</v>
       </c>
       <c r="E31">
-        <v>-17.054</v>
+        <v>-15.78</v>
       </c>
       <c r="F31">
-        <v>36.946</v>
+        <v>38.22</v>
       </c>
       <c r="G31">
         <v>5.62</v>
@@ -3829,28 +3829,28 @@
         <v>11.52</v>
       </c>
       <c r="M31">
-        <v>2.0431138</v>
+        <v>2.113566</v>
       </c>
       <c r="N31">
-        <v>9.476886199999999</v>
+        <v>9.406433999999999</v>
       </c>
       <c r="O31">
-        <v>3.316910169999999</v>
+        <v>3.2922519</v>
       </c>
       <c r="P31">
-        <v>6.159976029999999</v>
+        <v>6.114182099999999</v>
       </c>
       <c r="Q31">
-        <v>6.339976029999999</v>
+        <v>6.294182099999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1331984047096871</v>
+        <v>0.1341016396736953</v>
       </c>
       <c r="T31">
-        <v>1.600732475309875</v>
+        <v>1.617275540878703</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.638452444499175</v>
+        <v>5.450504029682536</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1046546477715867</v>
+        <v>0.1043143781992956</v>
       </c>
       <c r="C32">
-        <v>86.6622679997172</v>
+        <v>86.08179533729768</v>
       </c>
       <c r="D32">
-        <v>119.2622679997172</v>
+        <v>119.9557953372977</v>
       </c>
       <c r="E32">
-        <v>-15.78</v>
+        <v>-14.506</v>
       </c>
       <c r="F32">
-        <v>38.22</v>
+        <v>39.494</v>
       </c>
       <c r="G32">
         <v>5.62</v>
@@ -3911,28 +3911,28 @@
         <v>11.52</v>
       </c>
       <c r="M32">
-        <v>2.113566</v>
+        <v>2.1840182</v>
       </c>
       <c r="N32">
-        <v>9.406433999999999</v>
+        <v>9.335981799999999</v>
       </c>
       <c r="O32">
-        <v>3.2922519</v>
+        <v>3.267593629999999</v>
       </c>
       <c r="P32">
-        <v>6.114182099999999</v>
+        <v>6.06838817</v>
       </c>
       <c r="Q32">
-        <v>6.294182099999999</v>
+        <v>6.248388169999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1341016396736953</v>
+        <v>0.135031055361298</v>
       </c>
       <c r="T32">
-        <v>1.617275540878703</v>
+        <v>1.634298115594453</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.450504029682536</v>
+        <v>5.274681319047615</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1043143781992956</v>
+        <v>0.1039741086270045</v>
       </c>
       <c r="C33">
-        <v>86.08179533729768</v>
+        <v>85.50943577729086</v>
       </c>
       <c r="D33">
-        <v>119.9557953372977</v>
+        <v>120.6574357772909</v>
       </c>
       <c r="E33">
-        <v>-14.506</v>
+        <v>-13.232</v>
       </c>
       <c r="F33">
-        <v>39.494</v>
+        <v>40.768</v>
       </c>
       <c r="G33">
         <v>5.62</v>
@@ -3993,28 +3993,28 @@
         <v>11.52</v>
       </c>
       <c r="M33">
-        <v>2.1840182</v>
+        <v>2.2544704</v>
       </c>
       <c r="N33">
-        <v>9.335981799999999</v>
+        <v>9.265529599999999</v>
       </c>
       <c r="O33">
-        <v>3.267593629999999</v>
+        <v>3.242935359999999</v>
       </c>
       <c r="P33">
-        <v>6.06838817</v>
+        <v>6.02259424</v>
       </c>
       <c r="Q33">
-        <v>6.248388169999999</v>
+        <v>6.20259424</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.135031055361298</v>
+        <v>0.1359878068044184</v>
       </c>
       <c r="T33">
-        <v>1.634298115594453</v>
+        <v>1.651821354272431</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.274681319047615</v>
+        <v>5.109847527827377</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1039741086270045</v>
+        <v>0.1036338390547134</v>
       </c>
       <c r="C34">
-        <v>85.50943577729086</v>
+        <v>84.9453325217702</v>
       </c>
       <c r="D34">
-        <v>120.6574357772909</v>
+        <v>121.3673325217702</v>
       </c>
       <c r="E34">
-        <v>-13.232</v>
+        <v>-11.958</v>
       </c>
       <c r="F34">
-        <v>40.768</v>
+        <v>42.042</v>
       </c>
       <c r="G34">
         <v>5.62</v>
@@ -4075,28 +4075,28 @@
         <v>11.52</v>
       </c>
       <c r="M34">
-        <v>2.2544704</v>
+        <v>2.3249226</v>
       </c>
       <c r="N34">
-        <v>9.265529599999999</v>
+        <v>9.195077399999999</v>
       </c>
       <c r="O34">
-        <v>3.242935359999999</v>
+        <v>3.21827709</v>
       </c>
       <c r="P34">
-        <v>6.02259424</v>
+        <v>5.97680031</v>
       </c>
       <c r="Q34">
-        <v>6.20259424</v>
+        <v>6.156800309999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1359878068044184</v>
+        <v>0.1369731179921095</v>
       </c>
       <c r="T34">
-        <v>1.651821354272431</v>
+        <v>1.669867674701991</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.109847527827377</v>
+        <v>4.955003663347759</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1036338390547134</v>
+        <v>0.1032935694824222</v>
       </c>
       <c r="C35">
-        <v>84.9453325217702</v>
+        <v>84.38963216291395</v>
       </c>
       <c r="D35">
-        <v>121.3673325217702</v>
+        <v>122.085632162914</v>
       </c>
       <c r="E35">
-        <v>-11.958</v>
+        <v>-10.684</v>
       </c>
       <c r="F35">
-        <v>42.042</v>
+        <v>43.316</v>
       </c>
       <c r="G35">
         <v>5.62</v>
@@ -4157,28 +4157,28 @@
         <v>11.52</v>
       </c>
       <c r="M35">
-        <v>2.3249226</v>
+        <v>2.3953748</v>
       </c>
       <c r="N35">
-        <v>9.195077399999999</v>
+        <v>9.124625199999999</v>
       </c>
       <c r="O35">
-        <v>3.21827709</v>
+        <v>3.193618819999999</v>
       </c>
       <c r="P35">
-        <v>5.97680031</v>
+        <v>5.931006379999999</v>
       </c>
       <c r="Q35">
-        <v>6.156800309999999</v>
+        <v>6.111006379999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1369731179921095</v>
+        <v>0.1379882870945792</v>
       </c>
       <c r="T35">
-        <v>1.669867674701991</v>
+        <v>1.688460853326386</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.955003663347759</v>
+        <v>4.80926826148459</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1032935694824222</v>
+        <v>0.1029532999101311</v>
       </c>
       <c r="C36">
-        <v>84.38963216291395</v>
+        <v>83.84248478392249</v>
       </c>
       <c r="D36">
-        <v>122.085632162914</v>
+        <v>122.8124847839225</v>
       </c>
       <c r="E36">
-        <v>-10.684</v>
+        <v>-9.409999999999997</v>
       </c>
       <c r="F36">
-        <v>43.316</v>
+        <v>44.59</v>
       </c>
       <c r="G36">
         <v>5.62</v>
@@ -4239,28 +4239,28 @@
         <v>11.52</v>
       </c>
       <c r="M36">
-        <v>2.3953748</v>
+        <v>2.465827</v>
       </c>
       <c r="N36">
-        <v>9.124625199999999</v>
+        <v>9.054172999999999</v>
       </c>
       <c r="O36">
-        <v>3.193618819999999</v>
+        <v>3.16896055</v>
       </c>
       <c r="P36">
-        <v>5.931006379999999</v>
+        <v>5.885212449999999</v>
       </c>
       <c r="Q36">
-        <v>6.111006379999999</v>
+        <v>6.065212449999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1379882870945792</v>
+        <v>0.1390346921694325</v>
       </c>
       <c r="T36">
-        <v>1.688460853326386</v>
+        <v>1.707626129754608</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.80926826148459</v>
+        <v>4.671860596870745</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1029532999101311</v>
+        <v>0.10261303033784</v>
       </c>
       <c r="C37">
-        <v>83.84248478392249</v>
+        <v>83.30404406356192</v>
       </c>
       <c r="D37">
-        <v>122.8124847839225</v>
+        <v>123.5480440635619</v>
       </c>
       <c r="E37">
-        <v>-9.409999999999997</v>
+        <v>-8.135999999999996</v>
       </c>
       <c r="F37">
-        <v>44.59</v>
+        <v>45.864</v>
       </c>
       <c r="G37">
         <v>5.62</v>
@@ -4321,28 +4321,28 @@
         <v>11.52</v>
       </c>
       <c r="M37">
-        <v>2.465827</v>
+        <v>2.536279200000001</v>
       </c>
       <c r="N37">
-        <v>9.054172999999999</v>
+        <v>8.983720799999999</v>
       </c>
       <c r="O37">
-        <v>3.16896055</v>
+        <v>3.144302279999999</v>
       </c>
       <c r="P37">
-        <v>5.885212449999999</v>
+        <v>5.839418519999999</v>
       </c>
       <c r="Q37">
-        <v>6.065212449999999</v>
+        <v>6.019418519999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1390346921694325</v>
+        <v>0.140113797402875</v>
       </c>
       <c r="T37">
-        <v>1.707626129754608</v>
+        <v>1.727390321071212</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.671860596870745</v>
+        <v>4.542086691402112</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.10261303033784</v>
+        <v>0.1028740107655489</v>
       </c>
       <c r="C38">
-        <v>83.30404406356186</v>
+        <v>81.46510003825486</v>
       </c>
       <c r="D38">
-        <v>123.5480440635619</v>
+        <v>122.9831000382549</v>
       </c>
       <c r="E38">
-        <v>-8.136000000000003</v>
+        <v>-6.862000000000002</v>
       </c>
       <c r="F38">
-        <v>45.864</v>
+        <v>47.138</v>
       </c>
       <c r="G38">
         <v>5.62</v>
@@ -4403,45 +4403,45 @@
         <v>11.52</v>
       </c>
       <c r="M38">
-        <v>2.5362792</v>
+        <v>2.7245764</v>
       </c>
       <c r="N38">
-        <v>8.9837208</v>
+        <v>8.795423599999999</v>
       </c>
       <c r="O38">
-        <v>3.14430228</v>
+        <v>3.07839826</v>
       </c>
       <c r="P38">
-        <v>5.839418520000001</v>
+        <v>5.717025339999999</v>
       </c>
       <c r="Q38">
-        <v>6.01941852</v>
+        <v>5.897025339999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.140113797402875</v>
+        <v>0.1412271599453157</v>
       </c>
       <c r="T38">
-        <v>1.727390321071212</v>
+        <v>1.747781947032788</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.35</v>
       </c>
       <c r="W38">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.542086691402114</v>
+        <v>4.228180204453066</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1028740107655489</v>
+        <v>0.1025499911932578</v>
       </c>
       <c r="C39">
-        <v>81.46510003825486</v>
+        <v>80.89328396173303</v>
       </c>
       <c r="D39">
-        <v>122.9831000382549</v>
+        <v>123.685283961733</v>
       </c>
       <c r="E39">
-        <v>-6.862000000000002</v>
+        <v>-5.587999999999994</v>
       </c>
       <c r="F39">
-        <v>47.138</v>
+        <v>48.41200000000001</v>
       </c>
       <c r="G39">
         <v>5.62</v>
@@ -4485,28 +4485,28 @@
         <v>11.52</v>
       </c>
       <c r="M39">
-        <v>2.7245764</v>
+        <v>2.7982136</v>
       </c>
       <c r="N39">
-        <v>8.795423599999999</v>
+        <v>8.721786399999999</v>
       </c>
       <c r="O39">
-        <v>3.07839826</v>
+        <v>3.052625239999999</v>
       </c>
       <c r="P39">
-        <v>5.717025339999999</v>
+        <v>5.66916116</v>
       </c>
       <c r="Q39">
-        <v>5.897025339999999</v>
+        <v>5.84916116</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1412271599453157</v>
+        <v>0.1423764374084803</v>
       </c>
       <c r="T39">
-        <v>1.747781947032788</v>
+        <v>1.768831367380221</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.228180204453066</v>
+        <v>4.11691230433588</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1025499911932578</v>
+        <v>0.1022259716209667</v>
       </c>
       <c r="C40">
-        <v>80.89328396173303</v>
+        <v>80.32953230406008</v>
       </c>
       <c r="D40">
-        <v>123.685283961733</v>
+        <v>124.3955323040601</v>
       </c>
       <c r="E40">
-        <v>-5.587999999999994</v>
+        <v>-4.313999999999993</v>
       </c>
       <c r="F40">
-        <v>48.41200000000001</v>
+        <v>49.68600000000001</v>
       </c>
       <c r="G40">
         <v>5.62</v>
@@ -4567,28 +4567,28 @@
         <v>11.52</v>
       </c>
       <c r="M40">
-        <v>2.7982136</v>
+        <v>2.871850800000001</v>
       </c>
       <c r="N40">
-        <v>8.721786399999999</v>
+        <v>8.648149199999999</v>
       </c>
       <c r="O40">
-        <v>3.052625239999999</v>
+        <v>3.026852219999999</v>
       </c>
       <c r="P40">
-        <v>5.66916116</v>
+        <v>5.621296979999999</v>
       </c>
       <c r="Q40">
-        <v>5.84916116</v>
+        <v>5.801296979999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1423764374084803</v>
+        <v>0.1435633960999453</v>
       </c>
       <c r="T40">
-        <v>1.768831367380221</v>
+        <v>1.790570932657079</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.11691230433588</v>
+        <v>4.011350450378549</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1022259716209667</v>
+        <v>0.1028119520486755</v>
       </c>
       <c r="C41">
-        <v>80.32953230406008</v>
+        <v>77.77696974646912</v>
       </c>
       <c r="D41">
-        <v>124.3955323040601</v>
+        <v>123.1169697464691</v>
       </c>
       <c r="E41">
-        <v>-4.313999999999993</v>
+        <v>-3.039999999999992</v>
       </c>
       <c r="F41">
-        <v>49.68600000000001</v>
+        <v>50.96000000000001</v>
       </c>
       <c r="G41">
         <v>5.62</v>
@@ -4649,45 +4649,45 @@
         <v>11.52</v>
       </c>
       <c r="M41">
-        <v>2.871850800000001</v>
+        <v>3.123848000000001</v>
       </c>
       <c r="N41">
-        <v>8.648149199999999</v>
+        <v>8.396151999999999</v>
       </c>
       <c r="O41">
-        <v>3.026852219999999</v>
+        <v>2.9386532</v>
       </c>
       <c r="P41">
-        <v>5.621296979999999</v>
+        <v>5.4574988</v>
       </c>
       <c r="Q41">
-        <v>5.801296979999999</v>
+        <v>5.637498799999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1435633960999453</v>
+        <v>0.1447899200811259</v>
       </c>
       <c r="T41">
-        <v>1.790570932657079</v>
+        <v>1.813035150109831</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.35</v>
       </c>
       <c r="W41">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.011350450378549</v>
+        <v>3.687759455645728</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1028119520486755</v>
+        <v>0.1025106824763844</v>
       </c>
       <c r="C42">
-        <v>77.77696974646912</v>
+        <v>77.15701577796847</v>
       </c>
       <c r="D42">
-        <v>123.1169697464691</v>
+        <v>123.7710157779685</v>
       </c>
       <c r="E42">
-        <v>-3.039999999999992</v>
+        <v>-1.765999999999991</v>
       </c>
       <c r="F42">
-        <v>50.96000000000001</v>
+        <v>52.23400000000001</v>
       </c>
       <c r="G42">
         <v>5.62</v>
@@ -4731,28 +4731,28 @@
         <v>11.52</v>
       </c>
       <c r="M42">
-        <v>3.123848000000001</v>
+        <v>3.201944200000001</v>
       </c>
       <c r="N42">
-        <v>8.396151999999999</v>
+        <v>8.3180558</v>
       </c>
       <c r="O42">
-        <v>2.9386532</v>
+        <v>2.91131953</v>
       </c>
       <c r="P42">
-        <v>5.4574988</v>
+        <v>5.40673627</v>
       </c>
       <c r="Q42">
-        <v>5.637498799999999</v>
+        <v>5.586736269999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1447899200811259</v>
+        <v>0.1460580211464143</v>
       </c>
       <c r="T42">
-        <v>1.813035150109831</v>
+        <v>1.836260866459287</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.687759455645728</v>
+        <v>3.597814103069004</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1025106824763844</v>
+        <v>0.1022094129040933</v>
       </c>
       <c r="C43">
-        <v>77.15701577796847</v>
+        <v>76.54404802535004</v>
       </c>
       <c r="D43">
-        <v>123.7710157779685</v>
+        <v>124.43204802535</v>
       </c>
       <c r="E43">
-        <v>-1.765999999999991</v>
+        <v>-0.4919999999999902</v>
       </c>
       <c r="F43">
-        <v>52.23400000000001</v>
+        <v>53.50800000000001</v>
       </c>
       <c r="G43">
         <v>5.62</v>
@@ -4813,28 +4813,28 @@
         <v>11.52</v>
       </c>
       <c r="M43">
-        <v>3.201944200000001</v>
+        <v>3.280040400000001</v>
       </c>
       <c r="N43">
-        <v>8.3180558</v>
+        <v>8.239959599999999</v>
       </c>
       <c r="O43">
-        <v>2.91131953</v>
+        <v>2.883985859999999</v>
       </c>
       <c r="P43">
-        <v>5.40673627</v>
+        <v>5.35597374</v>
       </c>
       <c r="Q43">
-        <v>5.586736269999999</v>
+        <v>5.535973739999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1460580211464143</v>
+        <v>0.1473698498346436</v>
       </c>
       <c r="T43">
-        <v>1.836260866459287</v>
+        <v>1.860287469579413</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.597814103069004</v>
+        <v>3.512151862519741</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1022094129040933</v>
+        <v>0.1026907433318022</v>
       </c>
       <c r="C44">
-        <v>76.54404802535001</v>
+        <v>74.21727691727321</v>
       </c>
       <c r="D44">
-        <v>124.43204802535</v>
+        <v>123.3792769172732</v>
       </c>
       <c r="E44">
-        <v>-0.4919999999999973</v>
+        <v>0.7820000000000036</v>
       </c>
       <c r="F44">
-        <v>53.508</v>
+        <v>54.782</v>
       </c>
       <c r="G44">
         <v>5.62</v>
@@ -4895,45 +4895,45 @@
         <v>11.52</v>
       </c>
       <c r="M44">
-        <v>3.2800404</v>
+        <v>3.5115262</v>
       </c>
       <c r="N44">
-        <v>8.239959599999999</v>
+        <v>8.008473799999999</v>
       </c>
       <c r="O44">
-        <v>2.883985859999999</v>
+        <v>2.802965829999999</v>
       </c>
       <c r="P44">
-        <v>5.35597374</v>
+        <v>5.205507969999999</v>
       </c>
       <c r="Q44">
-        <v>5.535973739999999</v>
+        <v>5.385507969999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1473698498346436</v>
+        <v>0.1487277075996529</v>
       </c>
       <c r="T44">
-        <v>1.860287469579413</v>
+        <v>1.88515711140551</v>
       </c>
       <c r="U44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.35</v>
       </c>
       <c r="W44">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.512151862519742</v>
+        <v>3.280624817778662</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1026907433318022</v>
+        <v>0.102407673759511</v>
       </c>
       <c r="C45">
-        <v>74.21727691727321</v>
+        <v>73.56024131144591</v>
       </c>
       <c r="D45">
-        <v>123.3792769172732</v>
+        <v>123.9962413114459</v>
       </c>
       <c r="E45">
-        <v>0.7820000000000036</v>
+        <v>2.056000000000004</v>
       </c>
       <c r="F45">
-        <v>54.782</v>
+        <v>56.056</v>
       </c>
       <c r="G45">
         <v>5.62</v>
@@ -4977,28 +4977,28 @@
         <v>11.52</v>
       </c>
       <c r="M45">
-        <v>3.5115262</v>
+        <v>3.593189600000001</v>
       </c>
       <c r="N45">
-        <v>8.008473799999999</v>
+        <v>7.926810399999999</v>
       </c>
       <c r="O45">
-        <v>2.802965829999999</v>
+        <v>2.774383639999999</v>
       </c>
       <c r="P45">
-        <v>5.205507969999999</v>
+        <v>5.152426759999999</v>
       </c>
       <c r="Q45">
-        <v>5.385507969999999</v>
+        <v>5.332426759999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1487277075996529</v>
+        <v>0.1501340602848411</v>
       </c>
       <c r="T45">
-        <v>1.88515711140551</v>
+        <v>1.910914954725395</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.280624817778662</v>
+        <v>3.206065162829147</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.102407673759511</v>
+        <v>0.1021246041872199</v>
       </c>
       <c r="C46">
-        <v>73.56024131144591</v>
+        <v>72.90940703982045</v>
       </c>
       <c r="D46">
-        <v>123.9962413114459</v>
+        <v>124.6194070398205</v>
       </c>
       <c r="E46">
-        <v>2.056000000000004</v>
+        <v>3.330000000000005</v>
       </c>
       <c r="F46">
-        <v>56.056</v>
+        <v>57.33000000000001</v>
       </c>
       <c r="G46">
         <v>5.62</v>
@@ -5059,28 +5059,28 @@
         <v>11.52</v>
       </c>
       <c r="M46">
-        <v>3.593189600000001</v>
+        <v>3.674853000000001</v>
       </c>
       <c r="N46">
-        <v>7.926810399999999</v>
+        <v>7.845146999999999</v>
       </c>
       <c r="O46">
-        <v>2.774383639999999</v>
+        <v>2.74580145</v>
       </c>
       <c r="P46">
-        <v>5.152426759999999</v>
+        <v>5.099345549999999</v>
       </c>
       <c r="Q46">
-        <v>5.332426759999999</v>
+        <v>5.279345549999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1501340602848411</v>
+        <v>0.1515915530676726</v>
       </c>
       <c r="T46">
-        <v>1.910914954725395</v>
+        <v>1.937609446893276</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.206065162829147</v>
+        <v>3.134819270321833</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1021246041872199</v>
+        <v>0.1018415346149288</v>
       </c>
       <c r="C47">
-        <v>72.90940703982045</v>
+        <v>72.2648680724692</v>
       </c>
       <c r="D47">
-        <v>124.6194070398205</v>
+        <v>125.2488680724692</v>
       </c>
       <c r="E47">
-        <v>3.330000000000005</v>
+        <v>4.604000000000006</v>
       </c>
       <c r="F47">
-        <v>57.33000000000001</v>
+        <v>58.60400000000001</v>
       </c>
       <c r="G47">
         <v>5.62</v>
@@ -5141,28 +5141,28 @@
         <v>11.52</v>
       </c>
       <c r="M47">
-        <v>3.674853000000001</v>
+        <v>3.756516400000001</v>
       </c>
       <c r="N47">
-        <v>7.845146999999999</v>
+        <v>7.763483599999999</v>
       </c>
       <c r="O47">
-        <v>2.74580145</v>
+        <v>2.717219259999999</v>
       </c>
       <c r="P47">
-        <v>5.099345549999999</v>
+        <v>5.04626434</v>
       </c>
       <c r="Q47">
-        <v>5.279345549999999</v>
+        <v>5.226264339999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1515915530676726</v>
+        <v>0.153103027064683</v>
       </c>
       <c r="T47">
-        <v>1.937609446893276</v>
+        <v>1.965292623956264</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.134819270321833</v>
+        <v>3.066671025314836</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1018415346149288</v>
+        <v>0.1015584650426377</v>
       </c>
       <c r="C48">
-        <v>72.2648680724692</v>
+        <v>71.62672028769981</v>
       </c>
       <c r="D48">
-        <v>125.2488680724692</v>
+        <v>125.8847202876998</v>
       </c>
       <c r="E48">
-        <v>4.604000000000006</v>
+        <v>5.878000000000007</v>
       </c>
       <c r="F48">
-        <v>58.60400000000001</v>
+        <v>59.87800000000001</v>
       </c>
       <c r="G48">
         <v>5.62</v>
@@ -5223,28 +5223,28 @@
         <v>11.52</v>
       </c>
       <c r="M48">
-        <v>3.756516400000001</v>
+        <v>3.838179800000001</v>
       </c>
       <c r="N48">
-        <v>7.763483599999999</v>
+        <v>7.681820199999999</v>
       </c>
       <c r="O48">
-        <v>2.717219259999999</v>
+        <v>2.68863707</v>
       </c>
       <c r="P48">
-        <v>5.04626434</v>
+        <v>4.993183129999999</v>
       </c>
       <c r="Q48">
-        <v>5.226264339999999</v>
+        <v>5.173183129999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.153103027064683</v>
+        <v>0.1546715378162975</v>
       </c>
       <c r="T48">
-        <v>1.965292623956264</v>
+        <v>1.994020449210308</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.066671025314836</v>
+        <v>3.001422705627287</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1015584650426377</v>
+        <v>0.1037089954703466</v>
       </c>
       <c r="C49">
-        <v>71.62672028769981</v>
+        <v>65.6778175517174</v>
       </c>
       <c r="D49">
-        <v>125.8847202876998</v>
+        <v>121.2098175517174</v>
       </c>
       <c r="E49">
-        <v>5.878000000000007</v>
+        <v>7.152000000000008</v>
       </c>
       <c r="F49">
-        <v>59.87800000000001</v>
+        <v>61.15200000000001</v>
       </c>
       <c r="G49">
         <v>5.62</v>
@@ -5305,45 +5305,45 @@
         <v>11.52</v>
       </c>
       <c r="M49">
-        <v>3.838179800000001</v>
+        <v>4.396828800000001</v>
       </c>
       <c r="N49">
-        <v>7.681820199999999</v>
+        <v>7.123171199999999</v>
       </c>
       <c r="O49">
-        <v>2.68863707</v>
+        <v>2.493109919999999</v>
       </c>
       <c r="P49">
-        <v>4.993183129999999</v>
+        <v>4.63006128</v>
       </c>
       <c r="Q49">
-        <v>5.173183129999999</v>
+        <v>4.810061279999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1546715378162975</v>
+        <v>0.1563003759045126</v>
       </c>
       <c r="T49">
-        <v>1.994020449210308</v>
+        <v>2.023853190820276</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.35</v>
       </c>
       <c r="W49">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.001422705627287</v>
+        <v>2.620070174212832</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1037089954703466</v>
+        <v>0.1034766258980555</v>
       </c>
       <c r="C50">
-        <v>65.6778175517174</v>
+        <v>64.89215182965799</v>
       </c>
       <c r="D50">
-        <v>121.2098175517174</v>
+        <v>121.698151829658</v>
       </c>
       <c r="E50">
-        <v>7.152000000000001</v>
+        <v>8.426000000000002</v>
       </c>
       <c r="F50">
-        <v>61.152</v>
+        <v>62.426</v>
       </c>
       <c r="G50">
         <v>5.62</v>
@@ -5387,28 +5387,28 @@
         <v>11.52</v>
       </c>
       <c r="M50">
-        <v>4.396828800000001</v>
+        <v>4.4884294</v>
       </c>
       <c r="N50">
-        <v>7.123171199999999</v>
+        <v>7.031570599999999</v>
       </c>
       <c r="O50">
-        <v>2.493109919999999</v>
+        <v>2.46104971</v>
       </c>
       <c r="P50">
-        <v>4.63006128</v>
+        <v>4.570520889999999</v>
       </c>
       <c r="Q50">
-        <v>4.810061279999999</v>
+        <v>4.750520889999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1563003759045126</v>
+        <v>0.1579930899961871</v>
       </c>
       <c r="T50">
-        <v>2.023853190820276</v>
+        <v>2.05485584386593</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.620070174212832</v>
+        <v>2.566599354330938</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1034766258980555</v>
+        <v>0.1032442563257643</v>
       </c>
       <c r="C51">
-        <v>64.89215182965799</v>
+        <v>64.11043686036518</v>
       </c>
       <c r="D51">
-        <v>121.698151829658</v>
+        <v>122.1904368603652</v>
       </c>
       <c r="E51">
-        <v>8.426000000000002</v>
+        <v>9.700000000000003</v>
       </c>
       <c r="F51">
-        <v>62.426</v>
+        <v>63.7</v>
       </c>
       <c r="G51">
         <v>5.62</v>
@@ -5469,28 +5469,28 @@
         <v>11.52</v>
       </c>
       <c r="M51">
-        <v>4.4884294</v>
+        <v>4.580030000000001</v>
       </c>
       <c r="N51">
-        <v>7.031570599999999</v>
+        <v>6.939969999999999</v>
       </c>
       <c r="O51">
-        <v>2.46104971</v>
+        <v>2.428989499999999</v>
       </c>
       <c r="P51">
-        <v>4.570520889999999</v>
+        <v>4.5109805</v>
       </c>
       <c r="Q51">
-        <v>4.750520889999999</v>
+        <v>4.690980499999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1579930899961871</v>
+        <v>0.1597535126515286</v>
       </c>
       <c r="T51">
-        <v>2.05485584386593</v>
+        <v>2.08709860303341</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.566599354330938</v>
+        <v>2.515267367244319</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1032442563257643</v>
+        <v>0.1043047367534732</v>
       </c>
       <c r="C52">
-        <v>64.11043686036518</v>
+        <v>60.62156377599183</v>
       </c>
       <c r="D52">
-        <v>122.1904368603652</v>
+        <v>119.9755637759918</v>
       </c>
       <c r="E52">
-        <v>9.700000000000003</v>
+        <v>10.974</v>
       </c>
       <c r="F52">
-        <v>63.7</v>
+        <v>64.974</v>
       </c>
       <c r="G52">
         <v>5.62</v>
@@ -5551,45 +5551,45 @@
         <v>11.52</v>
       </c>
       <c r="M52">
-        <v>4.580030000000001</v>
+        <v>4.925029200000001</v>
       </c>
       <c r="N52">
-        <v>6.939969999999999</v>
+        <v>6.594970799999999</v>
       </c>
       <c r="O52">
-        <v>2.428989499999999</v>
+        <v>2.308239779999999</v>
       </c>
       <c r="P52">
-        <v>4.5109805</v>
+        <v>4.28673102</v>
       </c>
       <c r="Q52">
-        <v>4.690980499999999</v>
+        <v>4.466731019999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1597535126515286</v>
+        <v>0.1615857892928024</v>
       </c>
       <c r="T52">
-        <v>2.08709860303341</v>
+        <v>2.120657393187317</v>
       </c>
       <c r="U52">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.35</v>
       </c>
       <c r="W52">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.515267367244319</v>
+        <v>2.339072426210183</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1043047367534732</v>
+        <v>0.1040977171811821</v>
       </c>
       <c r="C53">
-        <v>60.62156377599183</v>
+        <v>59.77360601399405</v>
       </c>
       <c r="D53">
-        <v>119.9755637759918</v>
+        <v>120.4016060139941</v>
       </c>
       <c r="E53">
-        <v>10.974</v>
+        <v>12.248</v>
       </c>
       <c r="F53">
-        <v>64.974</v>
+        <v>66.248</v>
       </c>
       <c r="G53">
         <v>5.62</v>
@@ -5633,28 +5633,28 @@
         <v>11.52</v>
       </c>
       <c r="M53">
-        <v>4.925029200000001</v>
+        <v>5.021598400000001</v>
       </c>
       <c r="N53">
-        <v>6.594970799999999</v>
+        <v>6.498401599999998</v>
       </c>
       <c r="O53">
-        <v>2.308239779999999</v>
+        <v>2.27444056</v>
       </c>
       <c r="P53">
-        <v>4.28673102</v>
+        <v>4.223961039999999</v>
       </c>
       <c r="Q53">
-        <v>4.466731019999999</v>
+        <v>4.403961039999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1615857892928024</v>
+        <v>0.1634944107941293</v>
       </c>
       <c r="T53">
-        <v>2.120657393187317</v>
+        <v>2.155614466264305</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.339072426210183</v>
+        <v>2.294090264167679</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1040977171811821</v>
+        <v>0.1038906976088909</v>
       </c>
       <c r="C54">
-        <v>59.77360601399405</v>
+        <v>58.92868485116003</v>
       </c>
       <c r="D54">
-        <v>120.4016060139941</v>
+        <v>120.83068485116</v>
       </c>
       <c r="E54">
-        <v>12.248</v>
+        <v>13.52200000000001</v>
       </c>
       <c r="F54">
-        <v>66.248</v>
+        <v>67.52200000000001</v>
       </c>
       <c r="G54">
         <v>5.62</v>
@@ -5715,28 +5715,28 @@
         <v>11.52</v>
       </c>
       <c r="M54">
-        <v>5.021598400000001</v>
+        <v>5.1181676</v>
       </c>
       <c r="N54">
-        <v>6.498401599999998</v>
+        <v>6.401832399999999</v>
       </c>
       <c r="O54">
-        <v>2.27444056</v>
+        <v>2.240641339999999</v>
       </c>
       <c r="P54">
-        <v>4.223961039999999</v>
+        <v>4.16119106</v>
       </c>
       <c r="Q54">
-        <v>4.403961039999999</v>
+        <v>4.34119106</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1634944107941293</v>
+        <v>0.1654842502316829</v>
       </c>
       <c r="T54">
-        <v>2.155614466264305</v>
+        <v>2.192059074365845</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.294090264167679</v>
+        <v>2.250805542202252</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1038906976088909</v>
+        <v>0.1036836780365998</v>
       </c>
       <c r="C55">
-        <v>58.92868485116003</v>
+        <v>58.08683286845968</v>
       </c>
       <c r="D55">
-        <v>120.83068485116</v>
+        <v>121.2628328684597</v>
       </c>
       <c r="E55">
-        <v>13.52200000000001</v>
+        <v>14.79600000000001</v>
       </c>
       <c r="F55">
-        <v>67.52200000000001</v>
+        <v>68.79600000000001</v>
       </c>
       <c r="G55">
         <v>5.62</v>
@@ -5797,28 +5797,28 @@
         <v>11.52</v>
       </c>
       <c r="M55">
-        <v>5.1181676</v>
+        <v>5.214736800000001</v>
       </c>
       <c r="N55">
-        <v>6.401832399999999</v>
+        <v>6.305263199999999</v>
       </c>
       <c r="O55">
-        <v>2.240641339999999</v>
+        <v>2.206842119999999</v>
       </c>
       <c r="P55">
-        <v>4.16119106</v>
+        <v>4.09842108</v>
       </c>
       <c r="Q55">
-        <v>4.34119106</v>
+        <v>4.278421079999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1654842502316829</v>
+        <v>0.1675606044273909</v>
       </c>
       <c r="T55">
-        <v>2.192059074365845</v>
+        <v>2.230088230645712</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.250805542202252</v>
+        <v>2.209123958087395</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1036836780365998</v>
+        <v>0.1034766584643087</v>
       </c>
       <c r="C56">
-        <v>58.08683286845968</v>
+        <v>57.24808311463636</v>
       </c>
       <c r="D56">
-        <v>121.2628328684597</v>
+        <v>121.6980831146364</v>
       </c>
       <c r="E56">
-        <v>14.79600000000001</v>
+        <v>16.07000000000001</v>
       </c>
       <c r="F56">
-        <v>68.79600000000001</v>
+        <v>70.07000000000001</v>
       </c>
       <c r="G56">
         <v>5.62</v>
@@ -5879,28 +5879,28 @@
         <v>11.52</v>
       </c>
       <c r="M56">
-        <v>5.214736800000001</v>
+        <v>5.311306000000001</v>
       </c>
       <c r="N56">
-        <v>6.305263199999999</v>
+        <v>6.208693999999999</v>
       </c>
       <c r="O56">
-        <v>2.206842119999999</v>
+        <v>2.1730429</v>
       </c>
       <c r="P56">
-        <v>4.09842108</v>
+        <v>4.035651099999999</v>
       </c>
       <c r="Q56">
-        <v>4.278421079999999</v>
+        <v>4.215651099999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1675606044273909</v>
+        <v>0.1697292410317972</v>
       </c>
       <c r="T56">
-        <v>2.230088230645712</v>
+        <v>2.269807571649129</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.209123958087395</v>
+        <v>2.168958067940352</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1034766584643087</v>
+        <v>0.1032696388920176</v>
       </c>
       <c r="C57">
-        <v>57.24808311463636</v>
+        <v>56.41246911463156</v>
       </c>
       <c r="D57">
-        <v>121.6980831146364</v>
+        <v>122.1364691146316</v>
       </c>
       <c r="E57">
-        <v>16.07000000000001</v>
+        <v>17.34400000000001</v>
       </c>
       <c r="F57">
-        <v>70.07000000000001</v>
+        <v>71.34400000000001</v>
       </c>
       <c r="G57">
         <v>5.62</v>
@@ -5961,28 +5961,28 @@
         <v>11.52</v>
       </c>
       <c r="M57">
-        <v>5.311306000000001</v>
+        <v>5.407875200000001</v>
       </c>
       <c r="N57">
-        <v>6.208693999999999</v>
+        <v>6.112124799999998</v>
       </c>
       <c r="O57">
-        <v>2.1730429</v>
+        <v>2.139243679999999</v>
       </c>
       <c r="P57">
-        <v>4.035651099999999</v>
+        <v>3.972881119999999</v>
       </c>
       <c r="Q57">
-        <v>4.215651099999999</v>
+        <v>4.152881119999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1697292410317972</v>
+        <v>0.1719964520273127</v>
       </c>
       <c r="T57">
-        <v>2.269807571649129</v>
+        <v>2.311332337243611</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.168958067940352</v>
+        <v>2.130226673869988</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1032696388920176</v>
+        <v>0.1030626193197265</v>
       </c>
       <c r="C58">
-        <v>56.41246911463156</v>
+        <v>55.58002487819313</v>
       </c>
       <c r="D58">
-        <v>122.1364691146316</v>
+        <v>122.5780248781931</v>
       </c>
       <c r="E58">
-        <v>17.34400000000001</v>
+        <v>18.61800000000001</v>
       </c>
       <c r="F58">
-        <v>71.34400000000001</v>
+        <v>72.61800000000001</v>
       </c>
       <c r="G58">
         <v>5.62</v>
@@ -6043,28 +6043,28 @@
         <v>11.52</v>
       </c>
       <c r="M58">
-        <v>5.407875200000001</v>
+        <v>5.504444400000001</v>
       </c>
       <c r="N58">
-        <v>6.112124799999998</v>
+        <v>6.015555599999998</v>
       </c>
       <c r="O58">
-        <v>2.139243679999999</v>
+        <v>2.105444459999999</v>
       </c>
       <c r="P58">
-        <v>3.972881119999999</v>
+        <v>3.910111139999999</v>
       </c>
       <c r="Q58">
-        <v>4.152881119999999</v>
+        <v>4.090111139999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1719964520273127</v>
+        <v>0.1743691146970383</v>
       </c>
       <c r="T58">
-        <v>2.311332337243611</v>
+        <v>2.354788487284348</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.130226673869988</v>
+        <v>2.092854276082795</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1030626193197265</v>
+        <v>0.1028555997474354</v>
       </c>
       <c r="C59">
-        <v>55.58002487819313</v>
+        <v>54.75078490867052</v>
       </c>
       <c r="D59">
-        <v>122.5780248781931</v>
+        <v>123.0227849086705</v>
       </c>
       <c r="E59">
-        <v>18.61800000000001</v>
+        <v>19.89200000000001</v>
       </c>
       <c r="F59">
-        <v>72.61800000000001</v>
+        <v>73.89200000000001</v>
       </c>
       <c r="G59">
         <v>5.62</v>
@@ -6125,28 +6125,28 @@
         <v>11.52</v>
       </c>
       <c r="M59">
-        <v>5.504444400000001</v>
+        <v>5.601013600000001</v>
       </c>
       <c r="N59">
-        <v>6.015555599999998</v>
+        <v>5.918986399999999</v>
       </c>
       <c r="O59">
-        <v>2.105444459999999</v>
+        <v>2.07164524</v>
       </c>
       <c r="P59">
-        <v>3.910111139999999</v>
+        <v>3.847341159999999</v>
       </c>
       <c r="Q59">
-        <v>4.090111139999999</v>
+        <v>4.027341159999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1743691146970383</v>
+        <v>0.1768547613034175</v>
       </c>
       <c r="T59">
-        <v>2.354788487284348</v>
+        <v>2.400313977803215</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.092854276082795</v>
+        <v>2.056770581667575</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1028555997474354</v>
+        <v>0.1026485801751442</v>
       </c>
       <c r="C60">
-        <v>54.75078490867054</v>
+        <v>53.92478421200215</v>
       </c>
       <c r="D60">
-        <v>123.0227849086705</v>
+        <v>123.4707842120021</v>
       </c>
       <c r="E60">
-        <v>19.892</v>
+        <v>21.166</v>
       </c>
       <c r="F60">
-        <v>73.892</v>
+        <v>75.166</v>
       </c>
       <c r="G60">
         <v>5.62</v>
@@ -6207,28 +6207,28 @@
         <v>11.52</v>
       </c>
       <c r="M60">
-        <v>5.6010136</v>
+        <v>5.6975828</v>
       </c>
       <c r="N60">
-        <v>5.9189864</v>
+        <v>5.822417199999999</v>
       </c>
       <c r="O60">
-        <v>2.07164524</v>
+        <v>2.037846019999999</v>
       </c>
       <c r="P60">
-        <v>3.84734116</v>
+        <v>3.78457118</v>
       </c>
       <c r="Q60">
-        <v>4.02734116</v>
+        <v>3.96457118</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1768547613034175</v>
+        <v>0.1794616589637664</v>
       </c>
       <c r="T60">
-        <v>2.400313977803215</v>
+        <v>2.448060223957148</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.056770581667575</v>
+        <v>2.021910063334226</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1026485801751442</v>
+        <v>0.1079795606028531</v>
       </c>
       <c r="C61">
-        <v>53.92478421200215</v>
+        <v>42.0649851544603</v>
       </c>
       <c r="D61">
-        <v>123.4707842120021</v>
+        <v>112.8849851544603</v>
       </c>
       <c r="E61">
-        <v>21.166</v>
+        <v>22.44</v>
       </c>
       <c r="F61">
-        <v>75.166</v>
+        <v>76.44</v>
       </c>
       <c r="G61">
         <v>5.62</v>
@@ -6289,45 +6289,45 @@
         <v>11.52</v>
       </c>
       <c r="M61">
-        <v>5.6975828</v>
+        <v>6.8796</v>
       </c>
       <c r="N61">
-        <v>5.822417199999999</v>
+        <v>4.6404</v>
       </c>
       <c r="O61">
-        <v>2.037846019999999</v>
+        <v>1.62414</v>
       </c>
       <c r="P61">
-        <v>3.78457118</v>
+        <v>3.01626</v>
       </c>
       <c r="Q61">
-        <v>3.96457118</v>
+        <v>3.19626</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1794616589637664</v>
+        <v>0.1821989015071327</v>
       </c>
       <c r="T61">
-        <v>2.448060223957148</v>
+        <v>2.498193782418778</v>
       </c>
       <c r="U61">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V61">
         <v>0.35</v>
       </c>
       <c r="W61">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.021910063334226</v>
+        <v>1.674515960230246</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1079795606028531</v>
+        <v>0.107864841030562</v>
       </c>
       <c r="C62">
-        <v>42.0649851544603</v>
+        <v>40.99963979692741</v>
       </c>
       <c r="D62">
-        <v>112.8849851544603</v>
+        <v>113.0936397969274</v>
       </c>
       <c r="E62">
-        <v>22.44</v>
+        <v>23.714</v>
       </c>
       <c r="F62">
-        <v>76.44</v>
+        <v>77.714</v>
       </c>
       <c r="G62">
         <v>5.62</v>
@@ -6371,28 +6371,28 @@
         <v>11.52</v>
       </c>
       <c r="M62">
-        <v>6.8796</v>
+        <v>6.99426</v>
       </c>
       <c r="N62">
-        <v>4.6404</v>
+        <v>4.52574</v>
       </c>
       <c r="O62">
-        <v>1.62414</v>
+        <v>1.584009</v>
       </c>
       <c r="P62">
-        <v>3.01626</v>
+        <v>2.941731</v>
       </c>
       <c r="Q62">
-        <v>3.19626</v>
+        <v>3.121731</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1821989015071327</v>
+        <v>0.1850765154629794</v>
       </c>
       <c r="T62">
-        <v>2.498193782418778</v>
+        <v>2.55089829259639</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.674515960230246</v>
+        <v>1.647064878914996</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.107864841030562</v>
+        <v>0.1077501214582709</v>
       </c>
       <c r="C63">
-        <v>40.99963979692741</v>
+        <v>39.93506721500094</v>
       </c>
       <c r="D63">
-        <v>113.0936397969274</v>
+        <v>113.3030672150009</v>
       </c>
       <c r="E63">
-        <v>23.714</v>
+        <v>24.988</v>
       </c>
       <c r="F63">
-        <v>77.714</v>
+        <v>78.988</v>
       </c>
       <c r="G63">
         <v>5.62</v>
@@ -6453,28 +6453,28 @@
         <v>11.52</v>
       </c>
       <c r="M63">
-        <v>6.99426</v>
+        <v>7.108919999999999</v>
       </c>
       <c r="N63">
-        <v>4.52574</v>
+        <v>4.41108</v>
       </c>
       <c r="O63">
-        <v>1.584009</v>
+        <v>1.543878</v>
       </c>
       <c r="P63">
-        <v>2.941731</v>
+        <v>2.867202</v>
       </c>
       <c r="Q63">
-        <v>3.121731</v>
+        <v>3.047202</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1850765154629794</v>
+        <v>0.1881055827849233</v>
       </c>
       <c r="T63">
-        <v>2.55089829259639</v>
+        <v>2.606376724362297</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.647064878914996</v>
+        <v>1.620499316351851</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1077501214582709</v>
+        <v>0.1076354018859797</v>
       </c>
       <c r="C64">
-        <v>39.93506721500094</v>
+        <v>38.87127170973595</v>
       </c>
       <c r="D64">
-        <v>113.3030672150009</v>
+        <v>113.5132717097359</v>
       </c>
       <c r="E64">
-        <v>24.988</v>
+        <v>26.262</v>
       </c>
       <c r="F64">
-        <v>78.988</v>
+        <v>80.262</v>
       </c>
       <c r="G64">
         <v>5.62</v>
@@ -6535,28 +6535,28 @@
         <v>11.52</v>
       </c>
       <c r="M64">
-        <v>7.108919999999999</v>
+        <v>7.22358</v>
       </c>
       <c r="N64">
-        <v>4.41108</v>
+        <v>4.296419999999999</v>
       </c>
       <c r="O64">
-        <v>1.543878</v>
+        <v>1.503747</v>
       </c>
       <c r="P64">
-        <v>2.867202</v>
+        <v>2.792673</v>
       </c>
       <c r="Q64">
-        <v>3.047202</v>
+        <v>2.972673</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1881055827849233</v>
+        <v>0.1912983834756209</v>
       </c>
       <c r="T64">
-        <v>2.606376724362297</v>
+        <v>2.664853990277712</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.620499316351851</v>
+        <v>1.594777104981187</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1076354018859797</v>
+        <v>0.1075206823136886</v>
       </c>
       <c r="C65">
-        <v>38.87127170973595</v>
+        <v>37.80825761416457</v>
       </c>
       <c r="D65">
-        <v>113.5132717097359</v>
+        <v>113.7242576141646</v>
       </c>
       <c r="E65">
-        <v>26.262</v>
+        <v>27.536</v>
       </c>
       <c r="F65">
-        <v>80.262</v>
+        <v>81.536</v>
       </c>
       <c r="G65">
         <v>5.62</v>
@@ -6617,28 +6617,28 @@
         <v>11.52</v>
       </c>
       <c r="M65">
-        <v>7.22358</v>
+        <v>7.33824</v>
       </c>
       <c r="N65">
-        <v>4.296419999999999</v>
+        <v>4.18176</v>
       </c>
       <c r="O65">
-        <v>1.503747</v>
+        <v>1.463616</v>
       </c>
       <c r="P65">
-        <v>2.792673</v>
+        <v>2.718144</v>
       </c>
       <c r="Q65">
-        <v>2.972673</v>
+        <v>2.898144</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1912983834756209</v>
+        <v>0.1946685619824684</v>
       </c>
       <c r="T65">
-        <v>2.664853990277712</v>
+        <v>2.726579993188428</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.594777104981187</v>
+        <v>1.569858712715856</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1075206823136886</v>
+        <v>0.1074059627413975</v>
       </c>
       <c r="C66">
-        <v>37.80825761416457</v>
+        <v>36.74602929359418</v>
       </c>
       <c r="D66">
-        <v>113.7242576141646</v>
+        <v>113.9360292935942</v>
       </c>
       <c r="E66">
-        <v>27.536</v>
+        <v>28.81</v>
       </c>
       <c r="F66">
-        <v>81.536</v>
+        <v>82.81</v>
       </c>
       <c r="G66">
         <v>5.62</v>
@@ -6699,28 +6699,28 @@
         <v>11.52</v>
       </c>
       <c r="M66">
-        <v>7.33824</v>
+        <v>7.4529</v>
       </c>
       <c r="N66">
-        <v>4.18176</v>
+        <v>4.0671</v>
       </c>
       <c r="O66">
-        <v>1.463616</v>
+        <v>1.423485</v>
       </c>
       <c r="P66">
-        <v>2.718144</v>
+        <v>2.643615</v>
       </c>
       <c r="Q66">
-        <v>2.898144</v>
+        <v>2.823615</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1946685619824684</v>
+        <v>0.1982313221182786</v>
       </c>
       <c r="T66">
-        <v>2.726579993188428</v>
+        <v>2.791833196265471</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.569858712715856</v>
+        <v>1.545707040212535</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1074059627413975</v>
+        <v>0.1072912431691064</v>
       </c>
       <c r="C67">
-        <v>36.74602929359418</v>
+        <v>35.68459114590807</v>
       </c>
       <c r="D67">
-        <v>113.9360292935942</v>
+        <v>114.1485911459081</v>
       </c>
       <c r="E67">
-        <v>28.81</v>
+        <v>30.084</v>
       </c>
       <c r="F67">
-        <v>82.81</v>
+        <v>84.084</v>
       </c>
       <c r="G67">
         <v>5.62</v>
@@ -6781,28 +6781,28 @@
         <v>11.52</v>
       </c>
       <c r="M67">
-        <v>7.4529</v>
+        <v>7.56756</v>
       </c>
       <c r="N67">
-        <v>4.0671</v>
+        <v>3.952439999999999</v>
       </c>
       <c r="O67">
-        <v>1.423485</v>
+        <v>1.383354</v>
       </c>
       <c r="P67">
-        <v>2.643615</v>
+        <v>2.569086</v>
       </c>
       <c r="Q67">
-        <v>2.823615</v>
+        <v>2.749086</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1982313221182786</v>
+        <v>0.2020036563797246</v>
       </c>
       <c r="T67">
-        <v>2.791833196265471</v>
+        <v>2.860924823052927</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.545707040212535</v>
+        <v>1.522287236572951</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1072912431691064</v>
+        <v>0.1359952707498151</v>
       </c>
       <c r="C68">
-        <v>35.68459114590807</v>
+        <v>-1.916416703978598</v>
       </c>
       <c r="D68">
-        <v>114.1485911459081</v>
+        <v>77.8215832960214</v>
       </c>
       <c r="E68">
-        <v>30.084</v>
+        <v>31.358</v>
       </c>
       <c r="F68">
-        <v>84.084</v>
+        <v>85.358</v>
       </c>
       <c r="G68">
         <v>5.62</v>
@@ -6863,45 +6863,45 @@
         <v>11.52</v>
       </c>
       <c r="M68">
-        <v>7.56756</v>
+        <v>12.5305544</v>
       </c>
       <c r="N68">
-        <v>3.952439999999999</v>
+        <v>-1.010554400000002</v>
       </c>
       <c r="O68">
-        <v>1.383354</v>
+        <v>-0.3536940400000007</v>
       </c>
       <c r="P68">
-        <v>2.569086</v>
+        <v>-0.6568603600000014</v>
       </c>
       <c r="Q68">
-        <v>2.749086</v>
+        <v>-0.4768603600000014</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2020036563797246</v>
+        <v>0.2099624921156567</v>
       </c>
       <c r="T68">
-        <v>2.860924823052927</v>
+        <v>3.006693694584185</v>
       </c>
       <c r="U68">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.35</v>
+        <v>0.3217734723692672</v>
       </c>
       <c r="W68">
-        <v>0.0585</v>
+        <v>0.0995636542561916</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.522287236572951</v>
+        <v>0.9193527781979063</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1359952707498151</v>
+        <v>0.1370052707498151</v>
       </c>
       <c r="C69">
-        <v>-1.916416703978598</v>
+        <v>-4.052206801006946</v>
       </c>
       <c r="D69">
-        <v>77.8215832960214</v>
+        <v>76.95979319899305</v>
       </c>
       <c r="E69">
-        <v>31.358</v>
+        <v>32.63200000000001</v>
       </c>
       <c r="F69">
-        <v>85.358</v>
+        <v>86.63200000000001</v>
       </c>
       <c r="G69">
         <v>5.62</v>
@@ -6945,37 +6945,37 @@
         <v>11.52</v>
       </c>
       <c r="M69">
-        <v>12.5305544</v>
+        <v>12.7175776</v>
       </c>
       <c r="N69">
-        <v>-1.010554400000002</v>
+        <v>-1.197577600000002</v>
       </c>
       <c r="O69">
-        <v>-0.3536940400000007</v>
+        <v>-0.4191521600000008</v>
       </c>
       <c r="P69">
-        <v>-0.6568603600000014</v>
+        <v>-0.7784254400000017</v>
       </c>
       <c r="Q69">
-        <v>-0.4768603600000014</v>
+        <v>-0.5984254400000018</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2099624921156567</v>
+        <v>0.215092569994271</v>
       </c>
       <c r="T69">
-        <v>3.006693694584185</v>
+        <v>3.10065287253994</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.3217734723692672</v>
+        <v>0.3170415095403074</v>
       </c>
       <c r="W69">
-        <v>0.0995636542561916</v>
+        <v>0.1002583063994829</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9193527781979063</v>
+        <v>0.9058328844008782</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1370052707498151</v>
+        <v>0.1380152707498151</v>
       </c>
       <c r="C70">
-        <v>-4.052206801006946</v>
+        <v>-6.169119157051199</v>
       </c>
       <c r="D70">
-        <v>76.95979319899305</v>
+        <v>76.1168808429488</v>
       </c>
       <c r="E70">
-        <v>32.63200000000001</v>
+        <v>33.90600000000001</v>
       </c>
       <c r="F70">
-        <v>86.63200000000001</v>
+        <v>87.90600000000001</v>
       </c>
       <c r="G70">
         <v>5.62</v>
@@ -7027,37 +7027,37 @@
         <v>11.52</v>
       </c>
       <c r="M70">
-        <v>12.7175776</v>
+        <v>12.9046008</v>
       </c>
       <c r="N70">
-        <v>-1.197577600000002</v>
+        <v>-1.384600800000003</v>
       </c>
       <c r="O70">
-        <v>-0.4191521600000008</v>
+        <v>-0.484610280000001</v>
       </c>
       <c r="P70">
-        <v>-0.7784254400000017</v>
+        <v>-0.899990520000002</v>
       </c>
       <c r="Q70">
-        <v>-0.5984254400000018</v>
+        <v>-0.7199905200000021</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.215092569994271</v>
+        <v>0.2205536206392475</v>
       </c>
       <c r="T70">
-        <v>3.10065287253994</v>
+        <v>3.200673932944455</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.3170415095403074</v>
+        <v>0.3124467050542159</v>
       </c>
       <c r="W70">
-        <v>0.1002583063994829</v>
+        <v>0.1009328236980411</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9058328844008782</v>
+        <v>0.8927048715834741</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1380152707498151</v>
+        <v>0.1390252707498151</v>
       </c>
       <c r="C71">
-        <v>-6.169119157051199</v>
+        <v>-8.267767334879437</v>
       </c>
       <c r="D71">
-        <v>76.1168808429488</v>
+        <v>75.29223266512057</v>
       </c>
       <c r="E71">
-        <v>33.90600000000001</v>
+        <v>35.18000000000001</v>
       </c>
       <c r="F71">
-        <v>87.90600000000001</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="G71">
         <v>5.62</v>
@@ -7109,37 +7109,37 @@
         <v>11.52</v>
       </c>
       <c r="M71">
-        <v>12.9046008</v>
+        <v>13.091624</v>
       </c>
       <c r="N71">
-        <v>-1.384600800000003</v>
+        <v>-1.571624000000003</v>
       </c>
       <c r="O71">
-        <v>-0.484610280000001</v>
+        <v>-0.5500684000000011</v>
       </c>
       <c r="P71">
-        <v>-0.899990520000002</v>
+        <v>-1.021555600000002</v>
       </c>
       <c r="Q71">
-        <v>-0.7199905200000021</v>
+        <v>-0.8415556000000024</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2205536206392475</v>
+        <v>0.2263787413272224</v>
       </c>
       <c r="T71">
-        <v>3.200673932944455</v>
+        <v>3.307363064042603</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.3124467050542159</v>
+        <v>0.3079831806962985</v>
       </c>
       <c r="W71">
-        <v>0.1009328236980411</v>
+        <v>0.1015880690737834</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8927048715834741</v>
+        <v>0.8799519448465674</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1390252707498151</v>
+        <v>0.1400352707498151</v>
       </c>
       <c r="C72">
-        <v>-8.267767334879437</v>
+        <v>-10.34873859295183</v>
       </c>
       <c r="D72">
-        <v>75.29223266512057</v>
+        <v>74.48526140704817</v>
       </c>
       <c r="E72">
-        <v>35.18000000000001</v>
+        <v>36.45400000000001</v>
       </c>
       <c r="F72">
-        <v>89.18000000000001</v>
+        <v>90.45400000000001</v>
       </c>
       <c r="G72">
         <v>5.62</v>
@@ -7191,37 +7191,37 @@
         <v>11.52</v>
       </c>
       <c r="M72">
-        <v>13.091624</v>
+        <v>13.2786472</v>
       </c>
       <c r="N72">
-        <v>-1.571624000000003</v>
+        <v>-1.758647200000002</v>
       </c>
       <c r="O72">
-        <v>-0.5500684000000011</v>
+        <v>-0.6155265200000007</v>
       </c>
       <c r="P72">
-        <v>-1.021555600000002</v>
+        <v>-1.143120680000001</v>
       </c>
       <c r="Q72">
-        <v>-0.8415556000000024</v>
+        <v>-0.9631206800000014</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2263787413272224</v>
+        <v>0.232605594476437</v>
       </c>
       <c r="T72">
-        <v>3.307363064042603</v>
+        <v>3.421410066250969</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.3079831806962985</v>
+        <v>0.3036453894188859</v>
       </c>
       <c r="W72">
-        <v>0.1015880690737834</v>
+        <v>0.1022248568333076</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8799519448465674</v>
+        <v>0.8675582554825312</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1400352707498151</v>
+        <v>0.141045270749815</v>
       </c>
       <c r="C73">
-        <v>-10.3487385929518</v>
+        <v>-12.41259528010143</v>
       </c>
       <c r="D73">
-        <v>74.48526140704818</v>
+        <v>73.69540471989856</v>
       </c>
       <c r="E73">
-        <v>36.45399999999999</v>
+        <v>37.72799999999999</v>
       </c>
       <c r="F73">
-        <v>90.45399999999999</v>
+        <v>91.72799999999999</v>
       </c>
       <c r="G73">
         <v>5.62</v>
@@ -7273,37 +7273,37 @@
         <v>11.52</v>
       </c>
       <c r="M73">
-        <v>13.2786472</v>
+        <v>13.4656704</v>
       </c>
       <c r="N73">
-        <v>-1.7586472</v>
+        <v>-1.945670400000001</v>
       </c>
       <c r="O73">
-        <v>-0.6155265200000001</v>
+        <v>-0.6809846400000003</v>
       </c>
       <c r="P73">
-        <v>-1.14312068</v>
+        <v>-1.264685760000001</v>
       </c>
       <c r="Q73">
-        <v>-0.9631206800000005</v>
+        <v>-1.084685760000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2326055944764369</v>
+        <v>0.2392772228505953</v>
       </c>
       <c r="T73">
-        <v>3.421410066250968</v>
+        <v>3.543603282902788</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.303645389418886</v>
+        <v>0.2994280923436237</v>
       </c>
       <c r="W73">
-        <v>0.1022248568333076</v>
+        <v>0.1028439560439561</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8675582554825314</v>
+        <v>0.8555088352674962</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.141045270749815</v>
+        <v>0.1420552707498151</v>
       </c>
       <c r="C74">
-        <v>-12.41259528010143</v>
+        <v>-14.45987614240934</v>
       </c>
       <c r="D74">
-        <v>73.69540471989856</v>
+        <v>72.92212385759065</v>
       </c>
       <c r="E74">
-        <v>37.72799999999999</v>
+        <v>39.002</v>
       </c>
       <c r="F74">
-        <v>91.72799999999999</v>
+        <v>93.002</v>
       </c>
       <c r="G74">
         <v>5.62</v>
@@ -7355,37 +7355,37 @@
         <v>11.52</v>
       </c>
       <c r="M74">
-        <v>13.4656704</v>
+        <v>13.6526936</v>
       </c>
       <c r="N74">
-        <v>-1.945670400000001</v>
+        <v>-2.132693600000001</v>
       </c>
       <c r="O74">
-        <v>-0.6809846400000003</v>
+        <v>-0.7464427600000004</v>
       </c>
       <c r="P74">
-        <v>-1.264685760000001</v>
+        <v>-1.386250840000001</v>
       </c>
       <c r="Q74">
-        <v>-1.084685760000001</v>
+        <v>-1.206250840000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2392772228505953</v>
+        <v>0.2464430459191359</v>
       </c>
       <c r="T74">
-        <v>3.543603282902788</v>
+        <v>3.674847848936224</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2994280923436237</v>
+        <v>0.295326337653985</v>
       </c>
       <c r="W74">
-        <v>0.1028439560439561</v>
+        <v>0.103446093632395</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8555088352674962</v>
+        <v>0.8437895361542428</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1420552707498151</v>
+        <v>0.1430652707498151</v>
       </c>
       <c r="C75">
-        <v>-14.45987614240934</v>
+        <v>-16.49109754865631</v>
       </c>
       <c r="D75">
-        <v>72.92212385759065</v>
+        <v>72.16490245134368</v>
       </c>
       <c r="E75">
-        <v>39.002</v>
+        <v>40.276</v>
       </c>
       <c r="F75">
-        <v>93.002</v>
+        <v>94.276</v>
       </c>
       <c r="G75">
         <v>5.62</v>
@@ -7437,37 +7437,37 @@
         <v>11.52</v>
       </c>
       <c r="M75">
-        <v>13.6526936</v>
+        <v>13.8397168</v>
       </c>
       <c r="N75">
-        <v>-2.132693600000001</v>
+        <v>-2.319716800000002</v>
       </c>
       <c r="O75">
-        <v>-0.7464427600000004</v>
+        <v>-0.8119008800000006</v>
       </c>
       <c r="P75">
-        <v>-1.386250840000001</v>
+        <v>-1.507815920000001</v>
       </c>
       <c r="Q75">
-        <v>-1.206250840000001</v>
+        <v>-1.327815920000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2464430459191359</v>
+        <v>0.254160086146795</v>
       </c>
       <c r="T75">
-        <v>3.674847848936224</v>
+        <v>3.816188150818387</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.295326337653985</v>
+        <v>0.2913354411992014</v>
       </c>
       <c r="W75">
-        <v>0.103446093632395</v>
+        <v>0.1040319572319573</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8437895361542428</v>
+        <v>0.8323869748548611</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1430652707498151</v>
+        <v>0.1440752707498151</v>
       </c>
       <c r="C76">
-        <v>-16.49109754865631</v>
+        <v>-18.506754640209</v>
       </c>
       <c r="D76">
-        <v>72.16490245134368</v>
+        <v>71.42324535979101</v>
       </c>
       <c r="E76">
-        <v>40.276</v>
+        <v>41.55000000000001</v>
       </c>
       <c r="F76">
-        <v>94.276</v>
+        <v>95.55000000000001</v>
       </c>
       <c r="G76">
         <v>5.62</v>
@@ -7519,37 +7519,37 @@
         <v>11.52</v>
       </c>
       <c r="M76">
-        <v>13.8397168</v>
+        <v>14.02674</v>
       </c>
       <c r="N76">
-        <v>-2.319716800000002</v>
+        <v>-2.506740000000004</v>
       </c>
       <c r="O76">
-        <v>-0.8119008800000006</v>
+        <v>-0.8773590000000014</v>
       </c>
       <c r="P76">
-        <v>-1.507815920000001</v>
+        <v>-1.629381000000003</v>
       </c>
       <c r="Q76">
-        <v>-1.327815920000001</v>
+        <v>-1.449381000000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.254160086146795</v>
+        <v>0.2624944895926668</v>
       </c>
       <c r="T76">
-        <v>3.816188150818387</v>
+        <v>3.968835676851123</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2913354411992014</v>
+        <v>0.2874509686498786</v>
       </c>
       <c r="W76">
-        <v>0.1040319572319573</v>
+        <v>0.1046021978021978</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8323869748548611</v>
+        <v>0.8212884818567961</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1440752707498151</v>
+        <v>0.1450852707498151</v>
       </c>
       <c r="C77">
-        <v>-18.506754640209</v>
+        <v>-20.50732241072116</v>
       </c>
       <c r="D77">
-        <v>71.42324535979101</v>
+        <v>70.69667758927885</v>
       </c>
       <c r="E77">
-        <v>41.55000000000001</v>
+        <v>42.82400000000001</v>
       </c>
       <c r="F77">
-        <v>95.55000000000001</v>
+        <v>96.82400000000001</v>
       </c>
       <c r="G77">
         <v>5.62</v>
@@ -7601,37 +7601,37 @@
         <v>11.52</v>
       </c>
       <c r="M77">
-        <v>14.02674</v>
+        <v>14.2137632</v>
       </c>
       <c r="N77">
-        <v>-2.506740000000004</v>
+        <v>-2.693763200000003</v>
       </c>
       <c r="O77">
-        <v>-0.8773590000000014</v>
+        <v>-0.942817120000001</v>
       </c>
       <c r="P77">
-        <v>-1.629381000000003</v>
+        <v>-1.750946080000002</v>
       </c>
       <c r="Q77">
-        <v>-1.449381000000003</v>
+        <v>-1.570946080000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2624944895926668</v>
+        <v>0.2715234266590279</v>
       </c>
       <c r="T77">
-        <v>3.968835676851123</v>
+        <v>4.134203830053253</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2874509686498786</v>
+        <v>0.2836687190623802</v>
       </c>
       <c r="W77">
-        <v>0.1046021978021978</v>
+        <v>0.1051574320416426</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8212884818567961</v>
+        <v>0.8104820544639436</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1450852707498151</v>
+        <v>0.1916793149593584</v>
       </c>
       <c r="C78">
-        <v>-20.50732241072116</v>
+        <v>-44.36193380158491</v>
       </c>
       <c r="D78">
-        <v>70.69667758927885</v>
+        <v>48.1160661984151</v>
       </c>
       <c r="E78">
-        <v>42.82400000000001</v>
+        <v>44.09800000000001</v>
       </c>
       <c r="F78">
-        <v>96.82400000000001</v>
+        <v>98.09800000000001</v>
       </c>
       <c r="G78">
         <v>5.62</v>
@@ -7683,45 +7683,45 @@
         <v>11.52</v>
       </c>
       <c r="M78">
-        <v>14.2137632</v>
+        <v>19.6980784</v>
       </c>
       <c r="N78">
-        <v>-2.693763200000003</v>
+        <v>-8.178078400000004</v>
       </c>
       <c r="O78">
-        <v>-0.942817120000001</v>
+        <v>-2.862327440000001</v>
       </c>
       <c r="P78">
-        <v>-1.750946080000002</v>
+        <v>-5.315750960000003</v>
       </c>
       <c r="Q78">
-        <v>-1.570946080000002</v>
+        <v>-5.135750960000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2715234266590279</v>
+        <v>0.298746376555261</v>
       </c>
       <c r="T78">
-        <v>4.134203830053253</v>
+        <v>4.632801717707876</v>
       </c>
       <c r="U78">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.2836687190623802</v>
+        <v>0.2046900168698688</v>
       </c>
       <c r="W78">
-        <v>0.1051574320416426</v>
+        <v>0.1596982446125303</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.8104820544639436</v>
+        <v>0.5848286196281967</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1916793149593584</v>
+        <v>0.1932293149593584</v>
       </c>
       <c r="C79">
-        <v>-44.36193380158491</v>
+        <v>-46.14180268273721</v>
       </c>
       <c r="D79">
-        <v>48.1160661984151</v>
+        <v>47.6101973172628</v>
       </c>
       <c r="E79">
-        <v>44.09800000000001</v>
+        <v>45.37200000000001</v>
       </c>
       <c r="F79">
-        <v>98.09800000000001</v>
+        <v>99.37200000000001</v>
       </c>
       <c r="G79">
         <v>5.62</v>
@@ -7765,37 +7765,37 @@
         <v>11.52</v>
       </c>
       <c r="M79">
-        <v>19.6980784</v>
+        <v>19.9538976</v>
       </c>
       <c r="N79">
-        <v>-8.178078400000004</v>
+        <v>-8.433897600000005</v>
       </c>
       <c r="O79">
-        <v>-2.862327440000001</v>
+        <v>-2.951864160000002</v>
       </c>
       <c r="P79">
-        <v>-5.315750960000003</v>
+        <v>-5.482033440000004</v>
       </c>
       <c r="Q79">
-        <v>-5.135750960000003</v>
+        <v>-5.302033440000004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.298746376555261</v>
+        <v>0.3102439391259547</v>
       </c>
       <c r="T79">
-        <v>4.632801717707876</v>
+        <v>4.843383613967325</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.2046900168698688</v>
+        <v>0.2020657858843577</v>
       </c>
       <c r="W79">
-        <v>0.1596982446125303</v>
+        <v>0.160225190194421</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5848286196281967</v>
+        <v>0.5773308168124506</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1932293149593584</v>
+        <v>0.1947793149593584</v>
       </c>
       <c r="C80">
-        <v>-46.14180268273721</v>
+        <v>-47.9111453137722</v>
       </c>
       <c r="D80">
-        <v>47.6101973172628</v>
+        <v>47.11485468622782</v>
       </c>
       <c r="E80">
-        <v>45.37200000000001</v>
+        <v>46.64600000000002</v>
       </c>
       <c r="F80">
-        <v>99.37200000000001</v>
+        <v>100.646</v>
       </c>
       <c r="G80">
         <v>5.62</v>
@@ -7847,37 +7847,37 @@
         <v>11.52</v>
       </c>
       <c r="M80">
-        <v>19.9538976</v>
+        <v>20.2097168</v>
       </c>
       <c r="N80">
-        <v>-8.433897600000005</v>
+        <v>-8.689716800000003</v>
       </c>
       <c r="O80">
-        <v>-2.951864160000002</v>
+        <v>-3.041400880000001</v>
       </c>
       <c r="P80">
-        <v>-5.482033440000004</v>
+        <v>-5.648315920000002</v>
       </c>
       <c r="Q80">
-        <v>-5.302033440000004</v>
+        <v>-5.468315920000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3102439391259547</v>
+        <v>0.3228365076557621</v>
       </c>
       <c r="T80">
-        <v>4.843383613967325</v>
+        <v>5.074020928918151</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.2020657858843577</v>
+        <v>0.1995079911263279</v>
       </c>
       <c r="W80">
-        <v>0.160225190194421</v>
+        <v>0.1607387953818334</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5773308168124506</v>
+        <v>0.5700228317895082</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1947793149593584</v>
+        <v>0.1963293149593584</v>
       </c>
       <c r="C81">
-        <v>-47.9111453137722</v>
+        <v>-49.67028686100751</v>
       </c>
       <c r="D81">
-        <v>47.11485468622782</v>
+        <v>46.62971313899251</v>
       </c>
       <c r="E81">
-        <v>46.64600000000002</v>
+        <v>47.92000000000002</v>
       </c>
       <c r="F81">
-        <v>100.646</v>
+        <v>101.92</v>
       </c>
       <c r="G81">
         <v>5.62</v>
@@ -7929,37 +7929,37 @@
         <v>11.52</v>
       </c>
       <c r="M81">
-        <v>20.2097168</v>
+        <v>20.465536</v>
       </c>
       <c r="N81">
-        <v>-8.689716800000003</v>
+        <v>-8.945536000000004</v>
       </c>
       <c r="O81">
-        <v>-3.041400880000001</v>
+        <v>-3.130937600000001</v>
       </c>
       <c r="P81">
-        <v>-5.648315920000002</v>
+        <v>-5.814598400000003</v>
       </c>
       <c r="Q81">
-        <v>-5.468315920000002</v>
+        <v>-5.634598400000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3228365076557621</v>
+        <v>0.3366883330385502</v>
       </c>
       <c r="T81">
-        <v>5.074020928918151</v>
+        <v>5.327721975364058</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1995079911263279</v>
+        <v>0.1970141412372488</v>
       </c>
       <c r="W81">
-        <v>0.1607387953818334</v>
+        <v>0.1612395604395604</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5700228317895082</v>
+        <v>0.5628975463921393</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1963293149593584</v>
+        <v>0.1978793149593584</v>
       </c>
       <c r="C82">
-        <v>-49.67028686100751</v>
+        <v>-51.41953923431517</v>
       </c>
       <c r="D82">
-        <v>46.62971313899251</v>
+        <v>46.15446076568485</v>
       </c>
       <c r="E82">
-        <v>47.92000000000002</v>
+        <v>49.19400000000002</v>
       </c>
       <c r="F82">
-        <v>101.92</v>
+        <v>103.194</v>
       </c>
       <c r="G82">
         <v>5.62</v>
@@ -8011,37 +8011,37 @@
         <v>11.52</v>
       </c>
       <c r="M82">
-        <v>20.465536</v>
+        <v>20.7213552</v>
       </c>
       <c r="N82">
-        <v>-8.945536000000004</v>
+        <v>-9.201355200000005</v>
       </c>
       <c r="O82">
-        <v>-3.130937600000001</v>
+        <v>-3.220474320000002</v>
       </c>
       <c r="P82">
-        <v>-5.814598400000003</v>
+        <v>-5.980880880000004</v>
       </c>
       <c r="Q82">
-        <v>-5.634598400000003</v>
+        <v>-5.800880880000004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3366883330385502</v>
+        <v>0.351998245303737</v>
       </c>
       <c r="T82">
-        <v>5.327721975364058</v>
+        <v>5.608128395120062</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1970141412372488</v>
+        <v>0.1945818678886407</v>
       </c>
       <c r="W82">
-        <v>0.1612395604395604</v>
+        <v>0.1617279609279609</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5628975463921393</v>
+        <v>0.555948193967545</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1978793149593584</v>
+        <v>0.1994293149593584</v>
       </c>
       <c r="C83">
-        <v>-51.41953923431517</v>
+        <v>-53.15920175585761</v>
       </c>
       <c r="D83">
-        <v>46.15446076568485</v>
+        <v>45.68879824414241</v>
       </c>
       <c r="E83">
-        <v>49.19400000000002</v>
+        <v>50.46800000000002</v>
       </c>
       <c r="F83">
-        <v>103.194</v>
+        <v>104.468</v>
       </c>
       <c r="G83">
         <v>5.62</v>
@@ -8093,37 +8093,37 @@
         <v>11.52</v>
       </c>
       <c r="M83">
-        <v>20.7213552</v>
+        <v>20.9771744</v>
       </c>
       <c r="N83">
-        <v>-9.201355200000005</v>
+        <v>-9.457174400000003</v>
       </c>
       <c r="O83">
-        <v>-3.220474320000002</v>
+        <v>-3.310011040000001</v>
       </c>
       <c r="P83">
-        <v>-5.980880880000004</v>
+        <v>-6.147163360000002</v>
       </c>
       <c r="Q83">
-        <v>-5.800880880000004</v>
+        <v>-5.967163360000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.351998245303737</v>
+        <v>0.3690092589317224</v>
       </c>
       <c r="T83">
-        <v>5.608128395120062</v>
+        <v>5.919691083737843</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1945818678886407</v>
+        <v>0.1922089182802427</v>
       </c>
       <c r="W83">
-        <v>0.1617279609279609</v>
+        <v>0.1622044492093273</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.555948193967545</v>
+        <v>0.5491683379435506</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1994293149593584</v>
+        <v>0.2009793149593584</v>
       </c>
       <c r="C84">
-        <v>-53.15920175585761</v>
+        <v>-54.88956178874581</v>
       </c>
       <c r="D84">
-        <v>45.68879824414241</v>
+        <v>45.23243821125421</v>
       </c>
       <c r="E84">
-        <v>50.46800000000002</v>
+        <v>51.74200000000002</v>
       </c>
       <c r="F84">
-        <v>104.468</v>
+        <v>105.742</v>
       </c>
       <c r="G84">
         <v>5.62</v>
@@ -8175,37 +8175,37 @@
         <v>11.52</v>
       </c>
       <c r="M84">
-        <v>20.9771744</v>
+        <v>21.2329936</v>
       </c>
       <c r="N84">
-        <v>-9.457174400000003</v>
+        <v>-9.712993600000004</v>
       </c>
       <c r="O84">
-        <v>-3.310011040000001</v>
+        <v>-3.399547760000001</v>
       </c>
       <c r="P84">
-        <v>-6.147163360000002</v>
+        <v>-6.313445840000004</v>
       </c>
       <c r="Q84">
-        <v>-5.967163360000002</v>
+        <v>-6.133445840000004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3690092589317224</v>
+        <v>0.3880215682806473</v>
       </c>
       <c r="T84">
-        <v>5.919691083737843</v>
+        <v>6.267908206310657</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1922089182802427</v>
+        <v>0.1898931481804808</v>
       </c>
       <c r="W84">
-        <v>0.1622044492093273</v>
+        <v>0.1626694558453595</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5491683379435506</v>
+        <v>0.5425518519442307</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2009793149593584</v>
+        <v>0.2025293149593584</v>
       </c>
       <c r="C85">
-        <v>-54.88956178874581</v>
+        <v>-56.61089532839424</v>
       </c>
       <c r="D85">
-        <v>45.23243821125421</v>
+        <v>44.78510467160579</v>
       </c>
       <c r="E85">
-        <v>51.74200000000002</v>
+        <v>53.01600000000002</v>
       </c>
       <c r="F85">
-        <v>105.742</v>
+        <v>107.016</v>
       </c>
       <c r="G85">
         <v>5.62</v>
@@ -8257,37 +8257,37 @@
         <v>11.52</v>
       </c>
       <c r="M85">
-        <v>21.2329936</v>
+        <v>21.48881280000001</v>
       </c>
       <c r="N85">
-        <v>-9.712993600000004</v>
+        <v>-9.968812800000006</v>
       </c>
       <c r="O85">
-        <v>-3.399547760000001</v>
+        <v>-3.489084480000002</v>
       </c>
       <c r="P85">
-        <v>-6.313445840000004</v>
+        <v>-6.479728320000004</v>
       </c>
       <c r="Q85">
-        <v>-6.133445840000004</v>
+        <v>-6.299728320000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3880215682806473</v>
+        <v>0.4094104162981878</v>
       </c>
       <c r="T85">
-        <v>6.267908206310657</v>
+        <v>6.659652469205074</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1898931481804808</v>
+        <v>0.1876325154640464</v>
       </c>
       <c r="W85">
-        <v>0.1626694558453595</v>
+        <v>0.1631233908948195</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5425518519442307</v>
+        <v>0.536092901325847</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2025293149593584</v>
+        <v>0.2040793149593584</v>
       </c>
       <c r="C86">
-        <v>-56.61089532839421</v>
+        <v>-58.32346755912957</v>
       </c>
       <c r="D86">
-        <v>44.7851046716058</v>
+        <v>44.34653244087044</v>
       </c>
       <c r="E86">
-        <v>53.01600000000001</v>
+        <v>54.29000000000001</v>
       </c>
       <c r="F86">
-        <v>107.016</v>
+        <v>108.29</v>
       </c>
       <c r="G86">
         <v>5.62</v>
@@ -8339,37 +8339,37 @@
         <v>11.52</v>
       </c>
       <c r="M86">
-        <v>21.4888128</v>
+        <v>21.744632</v>
       </c>
       <c r="N86">
-        <v>-9.968812800000002</v>
+        <v>-10.224632</v>
       </c>
       <c r="O86">
-        <v>-3.489084480000001</v>
+        <v>-3.578621200000001</v>
       </c>
       <c r="P86">
-        <v>-6.479728320000001</v>
+        <v>-6.646010800000003</v>
       </c>
       <c r="Q86">
-        <v>-6.299728320000002</v>
+        <v>-6.466010800000003</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4094104162981875</v>
+        <v>0.4336511107180667</v>
       </c>
       <c r="T86">
-        <v>6.65965246920507</v>
+        <v>7.103629300485409</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1876325154640465</v>
+        <v>0.1854250741056459</v>
       </c>
       <c r="W86">
-        <v>0.1631233908948195</v>
+        <v>0.1635666451195863</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5360929013258471</v>
+        <v>0.5297859260161312</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2040793149593584</v>
+        <v>0.2056293149593584</v>
       </c>
       <c r="C87">
-        <v>-58.32346755912957</v>
+        <v>-60.02753337841202</v>
       </c>
       <c r="D87">
-        <v>44.34653244087044</v>
+        <v>43.91646662158799</v>
       </c>
       <c r="E87">
-        <v>54.29000000000001</v>
+        <v>55.56400000000001</v>
       </c>
       <c r="F87">
-        <v>108.29</v>
+        <v>109.564</v>
       </c>
       <c r="G87">
         <v>5.62</v>
@@ -8421,37 +8421,37 @@
         <v>11.52</v>
       </c>
       <c r="M87">
-        <v>21.744632</v>
+        <v>22.0004512</v>
       </c>
       <c r="N87">
-        <v>-10.224632</v>
+        <v>-10.4804512</v>
       </c>
       <c r="O87">
-        <v>-3.578621200000001</v>
+        <v>-3.66815792</v>
       </c>
       <c r="P87">
-        <v>-6.646010800000003</v>
+        <v>-6.81229328</v>
       </c>
       <c r="Q87">
-        <v>-6.466010800000003</v>
+        <v>-6.632293280000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4336511107180667</v>
+        <v>0.461354761483643</v>
       </c>
       <c r="T87">
-        <v>7.103629300485409</v>
+        <v>7.611031393377225</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1854250741056459</v>
+        <v>0.1832689685927896</v>
       </c>
       <c r="W87">
-        <v>0.1635666451195863</v>
+        <v>0.1639995911065679</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5297859260161312</v>
+        <v>0.5236256245508273</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2056293149593584</v>
+        <v>0.2071793149593584</v>
       </c>
       <c r="C88">
-        <v>-60.02753337841202</v>
+        <v>-61.72333789084662</v>
       </c>
       <c r="D88">
-        <v>43.91646662158799</v>
+        <v>43.49466210915339</v>
       </c>
       <c r="E88">
-        <v>55.56400000000001</v>
+        <v>56.83800000000001</v>
       </c>
       <c r="F88">
-        <v>109.564</v>
+        <v>110.838</v>
       </c>
       <c r="G88">
         <v>5.62</v>
@@ -8503,37 +8503,37 @@
         <v>11.52</v>
       </c>
       <c r="M88">
-        <v>22.0004512</v>
+        <v>22.2562704</v>
       </c>
       <c r="N88">
-        <v>-10.4804512</v>
+        <v>-10.7362704</v>
       </c>
       <c r="O88">
-        <v>-3.66815792</v>
+        <v>-3.75769464</v>
       </c>
       <c r="P88">
-        <v>-6.81229328</v>
+        <v>-6.978575760000002</v>
       </c>
       <c r="Q88">
-        <v>-6.632293280000001</v>
+        <v>-6.798575760000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.461354761483643</v>
+        <v>0.4933205123670001</v>
       </c>
       <c r="T88">
-        <v>7.611031393377225</v>
+        <v>8.196495346713935</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1832689685927896</v>
+        <v>0.1811624287239069</v>
       </c>
       <c r="W88">
-        <v>0.1639995911065679</v>
+        <v>0.1644225843122395</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5236256245508273</v>
+        <v>0.5176069392111626</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2071793149593584</v>
+        <v>0.2087293149593584</v>
       </c>
       <c r="C89">
-        <v>-61.72333789084662</v>
+        <v>-63.41111687399648</v>
       </c>
       <c r="D89">
-        <v>43.49466210915339</v>
+        <v>43.08088312600353</v>
       </c>
       <c r="E89">
-        <v>56.83800000000001</v>
+        <v>58.11200000000001</v>
       </c>
       <c r="F89">
-        <v>110.838</v>
+        <v>112.112</v>
       </c>
       <c r="G89">
         <v>5.62</v>
@@ -8585,37 +8585,37 @@
         <v>11.52</v>
       </c>
       <c r="M89">
-        <v>22.2562704</v>
+        <v>22.5120896</v>
       </c>
       <c r="N89">
-        <v>-10.7362704</v>
+        <v>-10.9920896</v>
       </c>
       <c r="O89">
-        <v>-3.75769464</v>
+        <v>-3.847231360000001</v>
       </c>
       <c r="P89">
-        <v>-6.978575760000002</v>
+        <v>-7.144858240000003</v>
       </c>
       <c r="Q89">
-        <v>-6.798575760000002</v>
+        <v>-6.964858240000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4933205123670001</v>
+        <v>0.5306138883975835</v>
       </c>
       <c r="T89">
-        <v>8.196495346713935</v>
+        <v>8.879536625606763</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1811624287239069</v>
+        <v>0.1791037647611353</v>
       </c>
       <c r="W89">
-        <v>0.1644225843122395</v>
+        <v>0.164835964035964</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5176069392111626</v>
+        <v>0.5117250421746722</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2087293149593584</v>
+        <v>0.2102793149593584</v>
       </c>
       <c r="C90">
-        <v>-63.41111687399648</v>
+        <v>-65.09109721785801</v>
       </c>
       <c r="D90">
-        <v>43.08088312600353</v>
+        <v>42.67490278214201</v>
       </c>
       <c r="E90">
-        <v>58.11200000000001</v>
+        <v>59.38600000000001</v>
       </c>
       <c r="F90">
-        <v>112.112</v>
+        <v>113.386</v>
       </c>
       <c r="G90">
         <v>5.62</v>
@@ -8667,37 +8667,37 @@
         <v>11.52</v>
       </c>
       <c r="M90">
-        <v>22.5120896</v>
+        <v>22.7679088</v>
       </c>
       <c r="N90">
-        <v>-10.9920896</v>
+        <v>-11.2479088</v>
       </c>
       <c r="O90">
-        <v>-3.847231360000001</v>
+        <v>-3.936768080000002</v>
       </c>
       <c r="P90">
-        <v>-7.144858240000003</v>
+        <v>-7.311140720000003</v>
       </c>
       <c r="Q90">
-        <v>-6.964858240000003</v>
+        <v>-7.131140720000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5306138883975835</v>
+        <v>0.5746878782519093</v>
       </c>
       <c r="T90">
-        <v>8.879536625606763</v>
+        <v>9.68676722793465</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1791037647611353</v>
+        <v>0.1770913629098865</v>
       </c>
       <c r="W90">
-        <v>0.164835964035964</v>
+        <v>0.1652400543276948</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5117250421746722</v>
+        <v>0.5059753225996758</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2102793149593584</v>
+        <v>0.2118293149593584</v>
       </c>
       <c r="C91">
-        <v>-65.09109721785801</v>
+        <v>-66.76349733971907</v>
       </c>
       <c r="D91">
-        <v>42.67490278214201</v>
+        <v>42.27650266028094</v>
       </c>
       <c r="E91">
-        <v>59.38600000000001</v>
+        <v>60.66000000000001</v>
       </c>
       <c r="F91">
-        <v>113.386</v>
+        <v>114.66</v>
       </c>
       <c r="G91">
         <v>5.62</v>
@@ -8749,37 +8749,37 @@
         <v>11.52</v>
       </c>
       <c r="M91">
-        <v>22.7679088</v>
+        <v>23.023728</v>
       </c>
       <c r="N91">
-        <v>-11.2479088</v>
+        <v>-11.503728</v>
       </c>
       <c r="O91">
-        <v>-3.936768080000002</v>
+        <v>-4.026304800000001</v>
       </c>
       <c r="P91">
-        <v>-7.311140720000003</v>
+        <v>-7.477423200000001</v>
       </c>
       <c r="Q91">
-        <v>-7.131140720000003</v>
+        <v>-7.297423200000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5746878782519093</v>
+        <v>0.6275766660771003</v>
       </c>
       <c r="T91">
-        <v>9.68676722793465</v>
+        <v>10.65544395072812</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1770913629098865</v>
+        <v>0.1751236810997767</v>
       </c>
       <c r="W91">
-        <v>0.1652400543276948</v>
+        <v>0.1656351648351648</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5059753225996758</v>
+        <v>0.5003533745707905</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2118293149593584</v>
+        <v>0.2468449951613998</v>
       </c>
       <c r="C92">
-        <v>-66.76349733971907</v>
+        <v>-75.40072712827823</v>
       </c>
       <c r="D92">
-        <v>42.27650266028094</v>
+        <v>34.91327287172178</v>
       </c>
       <c r="E92">
-        <v>60.66000000000001</v>
+        <v>61.93400000000001</v>
       </c>
       <c r="F92">
-        <v>114.66</v>
+        <v>115.934</v>
       </c>
       <c r="G92">
         <v>5.62</v>
@@ -8831,45 +8831,45 @@
         <v>11.52</v>
       </c>
       <c r="M92">
-        <v>23.023728</v>
+        <v>27.3372372</v>
       </c>
       <c r="N92">
-        <v>-11.503728</v>
+        <v>-15.8172372</v>
       </c>
       <c r="O92">
-        <v>-4.026304800000001</v>
+        <v>-5.536033020000001</v>
       </c>
       <c r="P92">
-        <v>-7.477423200000001</v>
+        <v>-10.28120418</v>
       </c>
       <c r="Q92">
-        <v>-7.297423200000002</v>
+        <v>-10.10120418</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6275766660771003</v>
+        <v>0.7101705201083492</v>
       </c>
       <c r="T92">
-        <v>10.65544395072812</v>
+        <v>12.16817939307389</v>
       </c>
       <c r="U92">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1751236810997767</v>
+        <v>0.1474911297912724</v>
       </c>
       <c r="W92">
-        <v>0.1656351648351648</v>
+        <v>0.201021591595218</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.5003533745707905</v>
+        <v>0.4214032279750639</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2468449951613998</v>
+        <v>0.2487449951613998</v>
       </c>
       <c r="C93">
-        <v>-75.40072712827823</v>
+        <v>-77.00159017017546</v>
       </c>
       <c r="D93">
-        <v>34.91327287172178</v>
+        <v>34.58640982982456</v>
       </c>
       <c r="E93">
-        <v>61.93400000000001</v>
+        <v>63.20800000000001</v>
       </c>
       <c r="F93">
-        <v>115.934</v>
+        <v>117.208</v>
       </c>
       <c r="G93">
         <v>5.62</v>
@@ -8913,37 +8913,37 @@
         <v>11.52</v>
       </c>
       <c r="M93">
-        <v>27.3372372</v>
+        <v>27.6376464</v>
       </c>
       <c r="N93">
-        <v>-15.8172372</v>
+        <v>-16.11764640000001</v>
       </c>
       <c r="O93">
-        <v>-5.536033020000001</v>
+        <v>-5.641176240000002</v>
       </c>
       <c r="P93">
-        <v>-10.28120418</v>
+        <v>-10.47647016</v>
       </c>
       <c r="Q93">
-        <v>-10.10120418</v>
+        <v>-10.29647016</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7101705201083492</v>
+        <v>0.7932168351218931</v>
       </c>
       <c r="T93">
-        <v>12.16817939307389</v>
+        <v>13.68920181720813</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1474911297912724</v>
+        <v>0.1458879653370194</v>
       </c>
       <c r="W93">
-        <v>0.201021591595218</v>
+        <v>0.2013996177735308</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4214032279750639</v>
+        <v>0.4168227581057697</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2487449951613998</v>
+        <v>0.2506449951613998</v>
       </c>
       <c r="C94">
-        <v>-77.00159017017546</v>
+        <v>-78.59638970264581</v>
       </c>
       <c r="D94">
-        <v>34.58640982982456</v>
+        <v>34.26561029735421</v>
       </c>
       <c r="E94">
-        <v>63.20800000000001</v>
+        <v>64.48200000000001</v>
       </c>
       <c r="F94">
-        <v>117.208</v>
+        <v>118.482</v>
       </c>
       <c r="G94">
         <v>5.62</v>
@@ -8995,37 +8995,37 @@
         <v>11.52</v>
       </c>
       <c r="M94">
-        <v>27.6376464</v>
+        <v>27.93805560000001</v>
       </c>
       <c r="N94">
-        <v>-16.11764640000001</v>
+        <v>-16.41805560000001</v>
       </c>
       <c r="O94">
-        <v>-5.641176240000002</v>
+        <v>-5.746319460000001</v>
       </c>
       <c r="P94">
-        <v>-10.47647016</v>
+        <v>-10.67173614</v>
       </c>
       <c r="Q94">
-        <v>-10.29647016</v>
+        <v>-10.49173614</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7932168351218931</v>
+        <v>0.8999906687107352</v>
       </c>
       <c r="T94">
-        <v>13.68920181720813</v>
+        <v>15.6448020768093</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1458879653370194</v>
+        <v>0.1443192775376966</v>
       </c>
       <c r="W94">
-        <v>0.2013996177735308</v>
+        <v>0.2017695143566112</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4168227581057697</v>
+        <v>0.4123407929648475</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2506449951613998</v>
+        <v>0.2525449951613998</v>
       </c>
       <c r="C95">
-        <v>-78.59638970264581</v>
+        <v>-80.18529289783149</v>
       </c>
       <c r="D95">
-        <v>34.26561029735421</v>
+        <v>33.95070710216853</v>
       </c>
       <c r="E95">
-        <v>64.48200000000001</v>
+        <v>65.75600000000001</v>
       </c>
       <c r="F95">
-        <v>118.482</v>
+        <v>119.756</v>
       </c>
       <c r="G95">
         <v>5.62</v>
@@ -9077,37 +9077,37 @@
         <v>11.52</v>
       </c>
       <c r="M95">
-        <v>27.93805560000001</v>
+        <v>28.23846480000001</v>
       </c>
       <c r="N95">
-        <v>-16.41805560000001</v>
+        <v>-16.71846480000001</v>
       </c>
       <c r="O95">
-        <v>-5.746319460000001</v>
+        <v>-5.851462680000002</v>
       </c>
       <c r="P95">
-        <v>-10.67173614</v>
+        <v>-10.86700212000001</v>
       </c>
       <c r="Q95">
-        <v>-10.49173614</v>
+        <v>-10.68700212000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8999906687107352</v>
+        <v>1.042355780162525</v>
       </c>
       <c r="T95">
-        <v>15.6448020768093</v>
+        <v>18.25226908961085</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1443192775376966</v>
+        <v>0.1427839660745296</v>
       </c>
       <c r="W95">
-        <v>0.2017695143566112</v>
+        <v>0.2021315407996259</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4123407929648475</v>
+        <v>0.4079541887843704</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2525449951613998</v>
+        <v>0.2544449951613998</v>
       </c>
       <c r="C96">
-        <v>-80.18529289783149</v>
+        <v>-81.76846083854447</v>
       </c>
       <c r="D96">
-        <v>33.95070710216853</v>
+        <v>33.64153916145555</v>
       </c>
       <c r="E96">
-        <v>65.75600000000001</v>
+        <v>67.03000000000002</v>
       </c>
       <c r="F96">
-        <v>119.756</v>
+        <v>121.03</v>
       </c>
       <c r="G96">
         <v>5.62</v>
@@ -9159,37 +9159,37 @@
         <v>11.52</v>
       </c>
       <c r="M96">
-        <v>28.23846480000001</v>
+        <v>28.538874</v>
       </c>
       <c r="N96">
-        <v>-16.71846480000001</v>
+        <v>-17.018874</v>
       </c>
       <c r="O96">
-        <v>-5.851462680000002</v>
+        <v>-5.956605900000001</v>
       </c>
       <c r="P96">
-        <v>-10.86700212000001</v>
+        <v>-11.0622681</v>
       </c>
       <c r="Q96">
-        <v>-10.68700212000001</v>
+        <v>-10.8822681</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.042355780162525</v>
+        <v>1.24166693619503</v>
       </c>
       <c r="T96">
-        <v>18.25226908961085</v>
+        <v>21.90272290753304</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1427839660745296</v>
+        <v>0.1412809769579556</v>
       </c>
       <c r="W96">
-        <v>0.2021315407996259</v>
+        <v>0.2024859456333141</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4079541887843704</v>
+        <v>0.4036599341655875</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2544449951613998</v>
+        <v>0.2563449951613998</v>
       </c>
       <c r="C97">
-        <v>-81.76846083854447</v>
+        <v>-83.34604879302312</v>
       </c>
       <c r="D97">
-        <v>33.64153916145555</v>
+        <v>33.3379512069769</v>
       </c>
       <c r="E97">
-        <v>67.03000000000002</v>
+        <v>68.30400000000002</v>
       </c>
       <c r="F97">
-        <v>121.03</v>
+        <v>122.304</v>
       </c>
       <c r="G97">
         <v>5.62</v>
@@ -9241,37 +9241,37 @@
         <v>11.52</v>
       </c>
       <c r="M97">
-        <v>28.538874</v>
+        <v>28.8392832</v>
       </c>
       <c r="N97">
-        <v>-17.018874</v>
+        <v>-17.3192832</v>
       </c>
       <c r="O97">
-        <v>-5.956605900000001</v>
+        <v>-6.061749120000001</v>
       </c>
       <c r="P97">
-        <v>-11.0622681</v>
+        <v>-11.25753408</v>
       </c>
       <c r="Q97">
-        <v>-10.8822681</v>
+        <v>-11.07753408</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.24166693619503</v>
+        <v>1.540633670243788</v>
       </c>
       <c r="T97">
-        <v>21.90272290753304</v>
+        <v>27.3784036344163</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1412809769579556</v>
+        <v>0.1398093001146436</v>
       </c>
       <c r="W97">
-        <v>0.2024859456333141</v>
+        <v>0.202832967032967</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4036599341655875</v>
+        <v>0.399455143184696</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2563449951613998</v>
+        <v>0.2582449951613998</v>
       </c>
       <c r="C98">
-        <v>-83.3460487930231</v>
+        <v>-84.91820647494512</v>
       </c>
       <c r="D98">
-        <v>33.3379512069769</v>
+        <v>33.03979352505489</v>
       </c>
       <c r="E98">
-        <v>68.304</v>
+        <v>69.578</v>
       </c>
       <c r="F98">
-        <v>122.304</v>
+        <v>123.578</v>
       </c>
       <c r="G98">
         <v>5.62</v>
@@ -9323,37 +9323,37 @@
         <v>11.52</v>
       </c>
       <c r="M98">
-        <v>28.8392832</v>
+        <v>29.1396924</v>
       </c>
       <c r="N98">
-        <v>-17.3192832</v>
+        <v>-17.6196924</v>
       </c>
       <c r="O98">
-        <v>-6.06174912</v>
+        <v>-6.16689234</v>
       </c>
       <c r="P98">
-        <v>-11.25753408</v>
+        <v>-11.45280006</v>
       </c>
       <c r="Q98">
-        <v>-11.07753408</v>
+        <v>-11.27280006</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.540633670243784</v>
+        <v>2.038911560325046</v>
       </c>
       <c r="T98">
-        <v>27.37840363441622</v>
+        <v>36.50453817922164</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1398093001146436</v>
+        <v>0.138367967123771</v>
       </c>
       <c r="W98">
-        <v>0.202832967032967</v>
+        <v>0.2031728333522148</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3994551431846961</v>
+        <v>0.3953370489250601</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2582449951613998</v>
+        <v>0.2601449951613998</v>
       </c>
       <c r="C99">
-        <v>-84.91820647494512</v>
+        <v>-86.48507828961161</v>
       </c>
       <c r="D99">
-        <v>33.03979352505489</v>
+        <v>32.74692171038839</v>
       </c>
       <c r="E99">
-        <v>69.578</v>
+        <v>70.852</v>
       </c>
       <c r="F99">
-        <v>123.578</v>
+        <v>124.852</v>
       </c>
       <c r="G99">
         <v>5.62</v>
@@ -9405,37 +9405,37 @@
         <v>11.52</v>
       </c>
       <c r="M99">
-        <v>29.1396924</v>
+        <v>29.4401016</v>
       </c>
       <c r="N99">
-        <v>-17.6196924</v>
+        <v>-17.9201016</v>
       </c>
       <c r="O99">
-        <v>-6.16689234</v>
+        <v>-6.272035560000001</v>
       </c>
       <c r="P99">
-        <v>-11.45280006</v>
+        <v>-11.64806604</v>
       </c>
       <c r="Q99">
-        <v>-11.27280006</v>
+        <v>-11.46806604</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.038911560325046</v>
+        <v>3.035467340487568</v>
       </c>
       <c r="T99">
-        <v>36.50453817922164</v>
+        <v>54.75680726883246</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.138367967123771</v>
+        <v>0.1369560490918958</v>
       </c>
       <c r="W99">
-        <v>0.2031728333522148</v>
+        <v>0.203505763624131</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3953370489250601</v>
+        <v>0.3913029974054165</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2601449951613998</v>
+        <v>0.2620449951613998</v>
       </c>
       <c r="C100">
-        <v>-86.48507828961161</v>
+        <v>-88.04680356715296</v>
       </c>
       <c r="D100">
-        <v>32.74692171038839</v>
+        <v>32.45919643284704</v>
       </c>
       <c r="E100">
-        <v>70.852</v>
+        <v>72.126</v>
       </c>
       <c r="F100">
-        <v>124.852</v>
+        <v>126.126</v>
       </c>
       <c r="G100">
         <v>5.62</v>
@@ -9487,37 +9487,37 @@
         <v>11.52</v>
       </c>
       <c r="M100">
-        <v>29.4401016</v>
+        <v>29.7405108</v>
       </c>
       <c r="N100">
-        <v>-17.9201016</v>
+        <v>-18.2205108</v>
       </c>
       <c r="O100">
-        <v>-6.272035560000001</v>
+        <v>-6.37717878</v>
       </c>
       <c r="P100">
-        <v>-11.64806604</v>
+        <v>-11.84333202</v>
       </c>
       <c r="Q100">
-        <v>-11.46806604</v>
+        <v>-11.66333202</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.035467340487568</v>
+        <v>6.025134680975137</v>
       </c>
       <c r="T100">
-        <v>54.75680726883246</v>
+        <v>109.5136145376649</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1369560490918958</v>
+        <v>0.1355726546566241</v>
       </c>
       <c r="W100">
-        <v>0.203505763624131</v>
+        <v>0.2038319680319681</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3913029974054165</v>
+        <v>0.3873504418760688</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2620449951613998</v>
-      </c>
-      <c r="C101">
-        <v>-88.04680356715296</v>
-      </c>
-      <c r="D101">
-        <v>32.45919643284704</v>
-      </c>
-      <c r="E101">
-        <v>72.126</v>
-      </c>
-      <c r="F101">
-        <v>126.126</v>
-      </c>
-      <c r="G101">
-        <v>5.62</v>
-      </c>
-      <c r="H101">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.7</v>
-      </c>
-      <c r="K101">
-        <v>0.18</v>
-      </c>
-      <c r="L101">
-        <v>11.52</v>
-      </c>
-      <c r="M101">
-        <v>29.7405108</v>
-      </c>
-      <c r="N101">
-        <v>-18.2205108</v>
-      </c>
-      <c r="O101">
-        <v>-6.37717878</v>
-      </c>
-      <c r="P101">
-        <v>-11.84333202</v>
-      </c>
-      <c r="Q101">
-        <v>-11.66333202</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.025134680975137</v>
-      </c>
-      <c r="T101">
-        <v>109.5136145376649</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1355726546566241</v>
-      </c>
-      <c r="W101">
-        <v>0.2038319680319681</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3873504418760688</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
